--- a/newtarifa.xlsx
+++ b/newtarifa.xlsx
@@ -534,12 +534,12 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Value1</t>
+          <t>Accesorio 1</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Value2</t>
+          <t>Accesorio 2</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
@@ -708,12 +708,8 @@
       <c r="Y3" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" t="n">
-        <v>126620.6458</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0.1219120143371879</v>
-      </c>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -791,12 +787,8 @@
       <c r="Y4" t="n">
         <v>0</v>
       </c>
-      <c r="Z4" t="n">
-        <v>118409.062</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>-2.459800585568318</v>
-      </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -874,8 +866,12 @@
       <c r="Y5" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>148528.9391</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-3.697400474080527</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1348,8 +1344,12 @@
       <c r="Y11" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
+      <c r="Z11" t="n">
+        <v>156081.7685999998</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-0.8114419173332447</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2217,8 +2217,12 @@
       <c r="Y22" t="n">
         <v>0</v>
       </c>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
+      <c r="Z22" t="n">
+        <v>129227.4764999999</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.453250602691271</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2296,8 +2300,12 @@
       <c r="Y23" t="n">
         <v>0</v>
       </c>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
+      <c r="Z23" t="n">
+        <v>126579.8559999999</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-0.09708115219154687</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2375,12 +2383,8 @@
       <c r="Y24" t="n">
         <v>0</v>
       </c>
-      <c r="Z24" t="n">
-        <v>144286.9404</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0.8382159984495642</v>
-      </c>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2537,12 +2541,8 @@
       <c r="Y26" t="n">
         <v>0</v>
       </c>
-      <c r="Z26" t="n">
-        <v>185678.3228999999</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.932512660342855</v>
-      </c>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3332,10 +3332,10 @@
         <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>168765.9202</v>
+        <v>171339.6072999999</v>
       </c>
       <c r="AA36" t="n">
-        <v>-7.20684089814025</v>
+        <v>-8.841749552235203</v>
       </c>
     </row>
     <row r="37">
@@ -3493,8 +3493,12 @@
       <c r="Y38" t="n">
         <v>0</v>
       </c>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr"/>
+      <c r="Z38" t="n">
+        <v>153054.8308999999</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-0.6693897956886689</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3651,8 +3655,12 @@
       <c r="Y40" t="n">
         <v>0</v>
       </c>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr"/>
+      <c r="Z40" t="n">
+        <v>189638.6933</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>19.45977484086782</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3730,12 +3738,8 @@
       <c r="Y41" t="n">
         <v>0</v>
       </c>
-      <c r="Z41" t="n">
-        <v>157736.4916</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>0.02950785905077192</v>
-      </c>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3892,12 +3896,8 @@
       <c r="Y43" t="n">
         <v>0</v>
       </c>
-      <c r="Z43" t="n">
-        <v>149806.9127</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>4.299603353575554</v>
-      </c>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4370,8 +4370,12 @@
       <c r="Y49" t="n">
         <v>0</v>
       </c>
-      <c r="Z49" t="inlineStr"/>
-      <c r="AA49" t="inlineStr"/>
+      <c r="Z49" t="n">
+        <v>100294.4271</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1.908645859190121</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4449,12 +4453,8 @@
       <c r="Y50" t="n">
         <v>0</v>
       </c>
-      <c r="Z50" t="n">
-        <v>147290.0298999999</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>-0.5405940842769263</v>
-      </c>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4611,8 +4611,12 @@
       <c r="Y52" t="n">
         <v>0</v>
       </c>
-      <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr"/>
+      <c r="Z52" t="n">
+        <v>98358.12019999989</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>1.979599288611124</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4690,12 +4694,8 @@
       <c r="Y53" t="n">
         <v>0</v>
       </c>
-      <c r="Z53" t="n">
-        <v>79058.57000000011</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>-1.288454959387299e-13</v>
-      </c>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5011,10 +5011,10 @@
         <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>101340.0197</v>
+        <v>102940.2178999999</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.2628166782898968</v>
+        <v>-1.312072113886508</v>
       </c>
     </row>
     <row r="58">
@@ -5251,8 +5251,12 @@
       <c r="Y60" t="n">
         <v>0</v>
       </c>
-      <c r="Z60" t="inlineStr"/>
-      <c r="AA60" t="inlineStr"/>
+      <c r="Z60" t="n">
+        <v>66905.08060000004</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>1.198901486097803</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -5330,12 +5334,8 @@
       <c r="Y61" t="n">
         <v>0</v>
       </c>
-      <c r="Z61" t="n">
-        <v>67716.94000000013</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>-1.934039504078325e-13</v>
-      </c>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -5413,12 +5413,8 @@
       <c r="Y62" t="n">
         <v>0</v>
       </c>
-      <c r="Z62" t="n">
-        <v>54085.61629999997</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>1.460886876528859</v>
-      </c>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -5497,10 +5493,10 @@
         <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>73709.63750000001</v>
+        <v>74108.45029999997</v>
       </c>
       <c r="AA63" t="n">
-        <v>-2.171402484394931</v>
+        <v>-2.724210291986225</v>
       </c>
     </row>
     <row r="64">
@@ -5579,8 +5575,12 @@
       <c r="Y64" t="n">
         <v>0</v>
       </c>
-      <c r="Z64" t="inlineStr"/>
-      <c r="AA64" t="inlineStr"/>
+      <c r="Z64" t="n">
+        <v>67716.94000000013</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>-1.934039504078325e-13</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -5816,8 +5816,12 @@
       <c r="Y67" t="n">
         <v>0</v>
       </c>
-      <c r="Z67" t="inlineStr"/>
-      <c r="AA67" t="inlineStr"/>
+      <c r="Z67" t="n">
+        <v>82667.25999999983</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>1.936329660763347e-13</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5974,12 +5978,8 @@
       <c r="Y69" t="n">
         <v>0</v>
       </c>
-      <c r="Z69" t="n">
-        <v>82141.19879999984</v>
-      </c>
-      <c r="AA69" t="n">
-        <v>0.6363597874178442</v>
-      </c>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -6057,12 +6057,8 @@
       <c r="Y70" t="n">
         <v>0</v>
       </c>
-      <c r="Z70" t="n">
-        <v>102965.8721000001</v>
-      </c>
-      <c r="AA70" t="n">
-        <v>1.404945271183135</v>
-      </c>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -6140,8 +6136,12 @@
       <c r="Y71" t="n">
         <v>0</v>
       </c>
-      <c r="Z71" t="inlineStr"/>
-      <c r="AA71" t="inlineStr"/>
+      <c r="Z71" t="n">
+        <v>153225.9921</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>-2.163929088924358</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -6298,8 +6298,12 @@
       <c r="Y73" t="n">
         <v>0</v>
       </c>
-      <c r="Z73" t="inlineStr"/>
-      <c r="AA73" t="inlineStr"/>
+      <c r="Z73" t="n">
+        <v>100322.1167999999</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>-0.8331999573035053</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -6377,8 +6381,12 @@
       <c r="Y74" t="n">
         <v>0</v>
       </c>
-      <c r="Z74" t="inlineStr"/>
-      <c r="AA74" t="inlineStr"/>
+      <c r="Z74" t="n">
+        <v>221157.6488</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>9.663912032072991</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -6456,8 +6464,12 @@
       <c r="Y75" t="n">
         <v>0</v>
       </c>
-      <c r="Z75" t="inlineStr"/>
-      <c r="AA75" t="inlineStr"/>
+      <c r="Z75" t="n">
+        <v>147925.9256999999</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-1.38615316098005</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -6535,12 +6547,8 @@
       <c r="Y76" t="n">
         <v>0</v>
       </c>
-      <c r="Z76" t="n">
-        <v>79058.57000000011</v>
-      </c>
-      <c r="AA76" t="n">
-        <v>-1.288454959387299e-13</v>
-      </c>
+      <c r="Z76" t="inlineStr"/>
+      <c r="AA76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -6698,10 +6706,10 @@
         <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>122525.6052000001</v>
+        <v>122262.2809000001</v>
       </c>
       <c r="AA78" t="n">
-        <v>0.8995588727718465</v>
+        <v>1.112539288146462</v>
       </c>
     </row>
     <row r="79">
@@ -6780,12 +6788,8 @@
       <c r="Y79" t="n">
         <v>0</v>
       </c>
-      <c r="Z79" t="n">
-        <v>95158.73519999994</v>
-      </c>
-      <c r="AA79" t="n">
-        <v>0.1517834780064614</v>
-      </c>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -6942,12 +6946,8 @@
       <c r="Y81" t="n">
         <v>0</v>
       </c>
-      <c r="Z81" t="n">
-        <v>144016.8219000001</v>
-      </c>
-      <c r="AA81" t="n">
-        <v>6.133803213472731</v>
-      </c>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -7183,8 +7183,12 @@
       <c r="Y84" t="n">
         <v>0</v>
       </c>
-      <c r="Z84" t="inlineStr"/>
-      <c r="AA84" t="inlineStr"/>
+      <c r="Z84" t="n">
+        <v>134477.9035000001</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>-0.5552861178228012</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -7499,8 +7503,12 @@
       <c r="Y88" t="n">
         <v>0</v>
       </c>
-      <c r="Z88" t="inlineStr"/>
-      <c r="AA88" t="inlineStr"/>
+      <c r="Z88" t="n">
+        <v>163487.7895000003</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>22.57406817088138</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -7578,8 +7586,12 @@
       <c r="Y89" t="n">
         <v>0</v>
       </c>
-      <c r="Z89" t="inlineStr"/>
-      <c r="AA89" t="inlineStr"/>
+      <c r="Z89" t="n">
+        <v>67716.94000000013</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>-1.934039504078325e-13</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -7657,8 +7669,12 @@
       <c r="Y90" t="n">
         <v>0</v>
       </c>
-      <c r="Z90" t="inlineStr"/>
-      <c r="AA90" t="inlineStr"/>
+      <c r="Z90" t="n">
+        <v>80556.81779999993</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>2.709286497324785</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -7973,12 +7989,8 @@
       <c r="Y94" t="n">
         <v>0</v>
       </c>
-      <c r="Z94" t="n">
-        <v>144220.6196999998</v>
-      </c>
-      <c r="AA94" t="n">
-        <v>0.4890315192842967</v>
-      </c>
+      <c r="Z94" t="inlineStr"/>
+      <c r="AA94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -8056,12 +8068,8 @@
       <c r="Y95" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" t="n">
-        <v>133609.3300999999</v>
-      </c>
-      <c r="AA95" t="n">
-        <v>-0.3798768178494609</v>
-      </c>
+      <c r="Z95" t="inlineStr"/>
+      <c r="AA95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -8297,8 +8305,12 @@
       <c r="Y98" t="n">
         <v>0</v>
       </c>
-      <c r="Z98" t="inlineStr"/>
-      <c r="AA98" t="inlineStr"/>
+      <c r="Z98" t="n">
+        <v>67716.94000000013</v>
+      </c>
+      <c r="AA98" t="n">
+        <v>-1.934039504078325e-13</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -8455,12 +8467,8 @@
       <c r="Y100" t="n">
         <v>0</v>
       </c>
-      <c r="Z100" t="n">
-        <v>97386.37349999989</v>
-      </c>
-      <c r="AA100" t="n">
-        <v>-1.50833250902721</v>
-      </c>
+      <c r="Z100" t="inlineStr"/>
+      <c r="AA100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -8538,12 +8546,8 @@
       <c r="Y101" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" t="n">
-        <v>145042.4125</v>
-      </c>
-      <c r="AA101" t="n">
-        <v>-0.3133096202073187</v>
-      </c>
+      <c r="Z101" t="inlineStr"/>
+      <c r="AA101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -8621,8 +8625,12 @@
       <c r="Y102" t="n">
         <v>0</v>
       </c>
-      <c r="Z102" t="inlineStr"/>
-      <c r="AA102" t="inlineStr"/>
+      <c r="Z102" t="n">
+        <v>146005.4117000001</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>0.9292682228427132</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -8779,8 +8787,12 @@
       <c r="Y104" t="n">
         <v>0</v>
       </c>
-      <c r="Z104" t="inlineStr"/>
-      <c r="AA104" t="inlineStr"/>
+      <c r="Z104" t="n">
+        <v>105826.4519</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>1.109999307569279</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -8858,12 +8870,8 @@
       <c r="Y105" t="n">
         <v>0</v>
       </c>
-      <c r="Z105" t="n">
-        <v>138734.0218000001</v>
-      </c>
-      <c r="AA105" t="n">
-        <v>2.834728927397983</v>
-      </c>
+      <c r="Z105" t="inlineStr"/>
+      <c r="AA105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -8941,12 +8949,8 @@
       <c r="Y106" t="n">
         <v>0</v>
       </c>
-      <c r="Z106" t="n">
-        <v>79058.57000000011</v>
-      </c>
-      <c r="AA106" t="n">
-        <v>-1.288454959387299e-13</v>
-      </c>
+      <c r="Z106" t="inlineStr"/>
+      <c r="AA106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -9024,12 +9028,8 @@
       <c r="Y107" t="n">
         <v>0</v>
       </c>
-      <c r="Z107" t="n">
-        <v>120452.3288</v>
-      </c>
-      <c r="AA107" t="n">
-        <v>1.191893281761025</v>
-      </c>
+      <c r="Z107" t="inlineStr"/>
+      <c r="AA107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -9502,8 +9502,12 @@
       <c r="Y113" t="n">
         <v>0</v>
       </c>
-      <c r="Z113" t="inlineStr"/>
-      <c r="AA113" t="inlineStr"/>
+      <c r="Z113" t="n">
+        <v>79058.57000000011</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>-1.288454959387299e-13</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -9581,12 +9585,8 @@
       <c r="Y114" t="n">
         <v>0</v>
       </c>
-      <c r="Z114" t="n">
-        <v>96899.24669999989</v>
-      </c>
-      <c r="AA114" t="n">
-        <v>-0.9873457390667756</v>
-      </c>
+      <c r="Z114" t="inlineStr"/>
+      <c r="AA114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -9664,8 +9664,12 @@
       <c r="Y115" t="n">
         <v>0</v>
       </c>
-      <c r="Z115" t="inlineStr"/>
-      <c r="AA115" t="inlineStr"/>
+      <c r="Z115" t="n">
+        <v>73058.59999999987</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>1.792632722982669e-13</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -9822,8 +9826,12 @@
       <c r="Y117" t="n">
         <v>0</v>
       </c>
-      <c r="Z117" t="inlineStr"/>
-      <c r="AA117" t="inlineStr"/>
+      <c r="Z117" t="n">
+        <v>158894.465</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>2.040878920589745</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -10138,8 +10146,12 @@
       <c r="Y121" t="n">
         <v>0</v>
       </c>
-      <c r="Z121" t="inlineStr"/>
-      <c r="AA121" t="inlineStr"/>
+      <c r="Z121" t="n">
+        <v>146937.4263999998</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.2495255591817824</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -10375,12 +10387,8 @@
       <c r="Y124" t="n">
         <v>0</v>
       </c>
-      <c r="Z124" t="n">
-        <v>15112.63170000001</v>
-      </c>
-      <c r="AA124" t="n">
-        <v>-2.002103806695537</v>
-      </c>
+      <c r="Z124" t="inlineStr"/>
+      <c r="AA124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -11091,10 +11099,10 @@
         <v>0</v>
       </c>
       <c r="Z133" t="n">
-        <v>256231.8190999999</v>
+        <v>231623.4786</v>
       </c>
       <c r="AA133" t="n">
-        <v>-13.03025830691286</v>
+        <v>-2.174904381747464</v>
       </c>
     </row>
     <row r="134">
@@ -11174,10 +11182,10 @@
         <v>0</v>
       </c>
       <c r="Z134" t="n">
-        <v>203208.1071</v>
+        <v>201416.5919999999</v>
       </c>
       <c r="AA134" t="n">
-        <v>7.024598333235331</v>
+        <v>7.844284311278582</v>
       </c>
     </row>
     <row r="135">
@@ -11256,12 +11264,8 @@
       <c r="Y135" t="n">
         <v>0</v>
       </c>
-      <c r="Z135" t="n">
-        <v>101280.5689</v>
-      </c>
-      <c r="AA135" t="n">
-        <v>-1.330636367429105</v>
-      </c>
+      <c r="Z135" t="inlineStr"/>
+      <c r="AA135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -11339,8 +11343,12 @@
       <c r="Y136" t="n">
         <v>0</v>
       </c>
-      <c r="Z136" t="inlineStr"/>
-      <c r="AA136" t="inlineStr"/>
+      <c r="Z136" t="n">
+        <v>142271.0191000001</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>-10.31616563388003</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -11418,12 +11426,8 @@
       <c r="Y137" t="n">
         <v>0</v>
       </c>
-      <c r="Z137" t="n">
-        <v>159435.7078999999</v>
-      </c>
-      <c r="AA137" t="n">
-        <v>2.386538346978373</v>
-      </c>
+      <c r="Z137" t="inlineStr"/>
+      <c r="AA137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -11501,8 +11505,12 @@
       <c r="Y138" t="n">
         <v>0</v>
       </c>
-      <c r="Z138" t="inlineStr"/>
-      <c r="AA138" t="inlineStr"/>
+      <c r="Z138" t="n">
+        <v>62577.71999999998</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>3.488122105207776e-14</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -11580,12 +11588,8 @@
       <c r="Y139" t="n">
         <v>0</v>
       </c>
-      <c r="Z139" t="n">
-        <v>67716.94000000013</v>
-      </c>
-      <c r="AA139" t="n">
-        <v>-1.934039504078325e-13</v>
-      </c>
+      <c r="Z139" t="inlineStr"/>
+      <c r="AA139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -11900,8 +11904,12 @@
       <c r="Y143" t="n">
         <v>0</v>
       </c>
-      <c r="Z143" t="inlineStr"/>
-      <c r="AA143" t="inlineStr"/>
+      <c r="Z143" t="n">
+        <v>79058.57000000011</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>-1.288454959387299e-13</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -12216,8 +12224,12 @@
       <c r="Y147" t="n">
         <v>0</v>
       </c>
-      <c r="Z147" t="inlineStr"/>
-      <c r="AA147" t="inlineStr"/>
+      <c r="Z147" t="n">
+        <v>79341.97469999993</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>-5.46362791699223</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -12296,10 +12308,10 @@
         <v>0</v>
       </c>
       <c r="Z148" t="n">
-        <v>175133.6055</v>
+        <v>167192.2072</v>
       </c>
       <c r="AA148" t="n">
-        <v>-8.957272743561411</v>
+        <v>-4.016627011589913</v>
       </c>
     </row>
     <row r="149">
@@ -12457,12 +12469,8 @@
       <c r="Y150" t="n">
         <v>0</v>
       </c>
-      <c r="Z150" t="n">
-        <v>91267.88930000005</v>
-      </c>
-      <c r="AA150" t="n">
-        <v>-0.1369377686161711</v>
-      </c>
+      <c r="Z150" t="inlineStr"/>
+      <c r="AA150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -12619,8 +12627,12 @@
       <c r="Y152" t="n">
         <v>0</v>
       </c>
-      <c r="Z152" t="inlineStr"/>
-      <c r="AA152" t="inlineStr"/>
+      <c r="Z152" t="n">
+        <v>190337.7155999999</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>2.651663843374251</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -12777,12 +12789,8 @@
       <c r="Y154" t="n">
         <v>0</v>
       </c>
-      <c r="Z154" t="n">
-        <v>99744.99369999998</v>
-      </c>
-      <c r="AA154" t="n">
-        <v>0.8423468270394219</v>
-      </c>
+      <c r="Z154" t="inlineStr"/>
+      <c r="AA154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -12939,8 +12947,12 @@
       <c r="Y156" t="n">
         <v>0</v>
       </c>
-      <c r="Z156" t="inlineStr"/>
-      <c r="AA156" t="inlineStr"/>
+      <c r="Z156" t="n">
+        <v>133727.4319</v>
+      </c>
+      <c r="AA156" t="n">
+        <v>0.1172191346906502</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -13018,12 +13030,8 @@
       <c r="Y157" t="n">
         <v>0</v>
       </c>
-      <c r="Z157" t="n">
-        <v>79058.57000000011</v>
-      </c>
-      <c r="AA157" t="n">
-        <v>-1.288454959387299e-13</v>
-      </c>
+      <c r="Z157" t="inlineStr"/>
+      <c r="AA157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -13101,12 +13109,8 @@
       <c r="Y158" t="n">
         <v>0</v>
       </c>
-      <c r="Z158" t="n">
-        <v>172838.1600000001</v>
-      </c>
-      <c r="AA158" t="n">
-        <v>0.4262348669626685</v>
-      </c>
+      <c r="Z158" t="inlineStr"/>
+      <c r="AA158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -13263,8 +13267,12 @@
       <c r="Y160" t="n">
         <v>0</v>
       </c>
-      <c r="Z160" t="inlineStr"/>
-      <c r="AA160" t="inlineStr"/>
+      <c r="Z160" t="n">
+        <v>244993.4043</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>13.31888858095627</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -13579,12 +13587,8 @@
       <c r="Y164" t="n">
         <v>0</v>
       </c>
-      <c r="Z164" t="n">
-        <v>152863.7501999998</v>
-      </c>
-      <c r="AA164" t="n">
-        <v>-0.04193084697549227</v>
-      </c>
+      <c r="Z164" t="inlineStr"/>
+      <c r="AA164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -13662,8 +13666,12 @@
       <c r="Y165" t="n">
         <v>0</v>
       </c>
-      <c r="Z165" t="inlineStr"/>
-      <c r="AA165" t="inlineStr"/>
+      <c r="Z165" t="n">
+        <v>67716.94000000013</v>
+      </c>
+      <c r="AA165" t="n">
+        <v>-1.934039504078325e-13</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -13820,8 +13828,12 @@
       <c r="Y167" t="n">
         <v>0</v>
       </c>
-      <c r="Z167" t="inlineStr"/>
-      <c r="AA167" t="inlineStr"/>
+      <c r="Z167" t="n">
+        <v>79058.57000000011</v>
+      </c>
+      <c r="AA167" t="n">
+        <v>-1.288454959387299e-13</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -14057,12 +14069,8 @@
       <c r="Y170" t="n">
         <v>0</v>
       </c>
-      <c r="Z170" t="n">
-        <v>34354.99680000004</v>
-      </c>
-      <c r="AA170" t="n">
-        <v>1.360859077945641</v>
-      </c>
+      <c r="Z170" t="inlineStr"/>
+      <c r="AA170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -14298,8 +14306,12 @@
       <c r="Y173" t="n">
         <v>0</v>
       </c>
-      <c r="Z173" t="inlineStr"/>
-      <c r="AA173" t="inlineStr"/>
+      <c r="Z173" t="n">
+        <v>143624.5072</v>
+      </c>
+      <c r="AA173" t="n">
+        <v>-0.1821156331231152</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -14377,12 +14389,8 @@
       <c r="Y174" t="n">
         <v>0</v>
       </c>
-      <c r="Z174" t="n">
-        <v>82667.25999999983</v>
-      </c>
-      <c r="AA174" t="n">
-        <v>1.936329660763347e-13</v>
-      </c>
+      <c r="Z174" t="inlineStr"/>
+      <c r="AA174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -14776,12 +14784,8 @@
       <c r="Y179" t="n">
         <v>0</v>
       </c>
-      <c r="Z179" t="n">
-        <v>166923.1167</v>
-      </c>
-      <c r="AA179" t="n">
-        <v>0.1001094676959333</v>
-      </c>
+      <c r="Z179" t="inlineStr"/>
+      <c r="AA179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -15333,12 +15337,8 @@
       <c r="Y186" t="n">
         <v>0</v>
       </c>
-      <c r="Z186" t="n">
-        <v>101546.1737</v>
-      </c>
-      <c r="AA186" t="n">
-        <v>4.314586577737612</v>
-      </c>
+      <c r="Z186" t="inlineStr"/>
+      <c r="AA186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -15574,8 +15574,12 @@
       <c r="Y189" t="n">
         <v>0</v>
       </c>
-      <c r="Z189" t="inlineStr"/>
-      <c r="AA189" t="inlineStr"/>
+      <c r="Z189" t="n">
+        <v>79510.89279999986</v>
+      </c>
+      <c r="AA189" t="n">
+        <v>3.818158724506097</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -15890,12 +15894,8 @@
       <c r="Y193" t="n">
         <v>0</v>
       </c>
-      <c r="Z193" t="n">
-        <v>67716.94000000013</v>
-      </c>
-      <c r="AA193" t="n">
-        <v>-1.934039504078325e-13</v>
-      </c>
+      <c r="Z193" t="inlineStr"/>
+      <c r="AA193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -15973,8 +15973,12 @@
       <c r="Y194" t="n">
         <v>0</v>
       </c>
-      <c r="Z194" t="inlineStr"/>
-      <c r="AA194" t="inlineStr"/>
+      <c r="Z194" t="n">
+        <v>133761.246</v>
+      </c>
+      <c r="AA194" t="n">
+        <v>-1.020989754802876</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -16767,12 +16771,8 @@
       <c r="Y204" t="n">
         <v>0</v>
       </c>
-      <c r="Z204" t="n">
-        <v>80149.1696000001</v>
-      </c>
-      <c r="AA204" t="n">
-        <v>-1.379483084503158</v>
-      </c>
+      <c r="Z204" t="inlineStr"/>
+      <c r="AA204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -17087,12 +17087,8 @@
       <c r="Y208" t="n">
         <v>0</v>
       </c>
-      <c r="Z208" t="n">
-        <v>146863.4065000002</v>
-      </c>
-      <c r="AA208" t="n">
-        <v>0.3565353293224786</v>
-      </c>
+      <c r="Z208" t="inlineStr"/>
+      <c r="AA208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -17407,12 +17403,8 @@
       <c r="Y212" t="n">
         <v>0</v>
       </c>
-      <c r="Z212" t="n">
-        <v>17795.08820000003</v>
-      </c>
-      <c r="AA212" t="n">
-        <v>0.8607539225128413</v>
-      </c>
+      <c r="Z212" t="inlineStr"/>
+      <c r="AA212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -18123,10 +18115,10 @@
         <v>0</v>
       </c>
       <c r="Z221" t="n">
-        <v>127950.5090000001</v>
+        <v>127326.0132999999</v>
       </c>
       <c r="AA221" t="n">
-        <v>0.4613386609189394</v>
+        <v>0.9471629571710916</v>
       </c>
     </row>
     <row r="222">
@@ -18205,8 +18197,12 @@
       <c r="Y222" t="n">
         <v>0</v>
       </c>
-      <c r="Z222" t="inlineStr"/>
-      <c r="AA222" t="inlineStr"/>
+      <c r="Z222" t="n">
+        <v>152681.3015</v>
+      </c>
+      <c r="AA222" t="n">
+        <v>-3.57602295205563</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -18443,10 +18439,10 @@
         <v>0</v>
       </c>
       <c r="Z225" t="n">
-        <v>111156.4557</v>
+        <v>116556.2046999998</v>
       </c>
       <c r="AA225" t="n">
-        <v>19.78840689039265</v>
+        <v>15.89189483489004</v>
       </c>
     </row>
     <row r="226">
@@ -18604,8 +18600,12 @@
       <c r="Y227" t="n">
         <v>0</v>
       </c>
-      <c r="Z227" t="inlineStr"/>
-      <c r="AA227" t="inlineStr"/>
+      <c r="Z227" t="n">
+        <v>157454.2546</v>
+      </c>
+      <c r="AA227" t="n">
+        <v>1.993041911858986</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -18842,10 +18842,10 @@
         <v>0</v>
       </c>
       <c r="Z230" t="n">
-        <v>124587.8155999998</v>
+        <v>124402.7251999998</v>
       </c>
       <c r="AA230" t="n">
-        <v>0.2232178452291508</v>
+        <v>0.3714484280577911</v>
       </c>
     </row>
     <row r="231">
@@ -18924,8 +18924,12 @@
       <c r="Y231" t="n">
         <v>0</v>
       </c>
-      <c r="Z231" t="inlineStr"/>
-      <c r="AA231" t="inlineStr"/>
+      <c r="Z231" t="n">
+        <v>166818.4606</v>
+      </c>
+      <c r="AA231" t="n">
+        <v>-0.2661028744997552</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -19082,12 +19086,8 @@
       <c r="Y233" t="n">
         <v>0</v>
       </c>
-      <c r="Z233" t="n">
-        <v>139947.9522000001</v>
-      </c>
-      <c r="AA233" t="n">
-        <v>-1.713042920843125</v>
-      </c>
+      <c r="Z233" t="inlineStr"/>
+      <c r="AA233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -19165,8 +19165,12 @@
       <c r="Y234" t="n">
         <v>0</v>
       </c>
-      <c r="Z234" t="inlineStr"/>
-      <c r="AA234" t="inlineStr"/>
+      <c r="Z234" t="n">
+        <v>156560.3385999999</v>
+      </c>
+      <c r="AA234" t="n">
+        <v>3.845745103581215</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -19323,12 +19327,8 @@
       <c r="Y236" t="n">
         <v>0</v>
       </c>
-      <c r="Z236" t="n">
-        <v>268298.1734</v>
-      </c>
-      <c r="AA236" t="n">
-        <v>-20.39500483423116</v>
-      </c>
+      <c r="Z236" t="inlineStr"/>
+      <c r="AA236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -20670,8 +20670,12 @@
       <c r="Y253" t="n">
         <v>0</v>
       </c>
-      <c r="Z253" t="inlineStr"/>
-      <c r="AA253" t="inlineStr"/>
+      <c r="Z253" t="n">
+        <v>30828.65399999998</v>
+      </c>
+      <c r="AA253" t="n">
+        <v>67.89367478819629</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -20829,10 +20833,10 @@
         <v>0</v>
       </c>
       <c r="Z255" t="n">
-        <v>117093.1876000001</v>
+        <v>114496.9941000001</v>
       </c>
       <c r="AA255" t="n">
-        <v>-0.2642537225377617</v>
+        <v>1.958808174846313</v>
       </c>
     </row>
     <row r="256">
@@ -21227,8 +21231,12 @@
       <c r="Y260" t="n">
         <v>0</v>
       </c>
-      <c r="Z260" t="inlineStr"/>
-      <c r="AA260" t="inlineStr"/>
+      <c r="Z260" t="n">
+        <v>42471.37700000001</v>
+      </c>
+      <c r="AA260" t="n">
+        <v>-1.275469167782067</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -21622,12 +21630,8 @@
       <c r="Y265" t="n">
         <v>0</v>
       </c>
-      <c r="Z265" t="n">
-        <v>133102.2411</v>
-      </c>
-      <c r="AA265" t="n">
-        <v>0.7684825281290099</v>
-      </c>
+      <c r="Z265" t="inlineStr"/>
+      <c r="AA265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -22416,8 +22420,12 @@
       <c r="Y275" t="n">
         <v>0</v>
       </c>
-      <c r="Z275" t="inlineStr"/>
-      <c r="AA275" t="inlineStr"/>
+      <c r="Z275" t="n">
+        <v>142802.1436</v>
+      </c>
+      <c r="AA275" t="n">
+        <v>1.195609553051108</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -22574,8 +22582,12 @@
       <c r="Y277" t="n">
         <v>0</v>
       </c>
-      <c r="Z277" t="inlineStr"/>
-      <c r="AA277" t="inlineStr"/>
+      <c r="Z277" t="n">
+        <v>155500.9930000001</v>
+      </c>
+      <c r="AA277" t="n">
+        <v>-3.223618501749663</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -22732,8 +22744,12 @@
       <c r="Y279" t="n">
         <v>0</v>
       </c>
-      <c r="Z279" t="inlineStr"/>
-      <c r="AA279" t="inlineStr"/>
+      <c r="Z279" t="n">
+        <v>130394.2876999999</v>
+      </c>
+      <c r="AA279" t="n">
+        <v>-3.177824484141603</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -22812,10 +22828,10 @@
         <v>0</v>
       </c>
       <c r="Z280" t="n">
-        <v>35775.74790000003</v>
+        <v>34049.64580000003</v>
       </c>
       <c r="AA280" t="n">
-        <v>-35.75660440650476</v>
+        <v>-29.20664322582075</v>
       </c>
     </row>
     <row r="281">
@@ -22894,8 +22910,12 @@
       <c r="Y281" t="n">
         <v>0</v>
       </c>
-      <c r="Z281" t="inlineStr"/>
-      <c r="AA281" t="inlineStr"/>
+      <c r="Z281" t="n">
+        <v>33018.52750000005</v>
+      </c>
+      <c r="AA281" t="n">
+        <v>-0.5510072450507428</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -22973,8 +22993,12 @@
       <c r="Y282" t="n">
         <v>0</v>
       </c>
-      <c r="Z282" t="inlineStr"/>
-      <c r="AA282" t="inlineStr"/>
+      <c r="Z282" t="n">
+        <v>79058.57000000011</v>
+      </c>
+      <c r="AA282" t="n">
+        <v>-1.288454959387299e-13</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -23052,12 +23076,8 @@
       <c r="Y283" t="n">
         <v>0</v>
       </c>
-      <c r="Z283" t="n">
-        <v>67716.94000000013</v>
-      </c>
-      <c r="AA283" t="n">
-        <v>-1.934039504078325e-13</v>
-      </c>
+      <c r="Z283" t="inlineStr"/>
+      <c r="AA283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -23135,12 +23155,8 @@
       <c r="Y284" t="n">
         <v>0</v>
       </c>
-      <c r="Z284" t="n">
-        <v>122489.4009</v>
-      </c>
-      <c r="AA284" t="n">
-        <v>0.6615451977987631</v>
-      </c>
+      <c r="Z284" t="inlineStr"/>
+      <c r="AA284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -23297,12 +23313,8 @@
       <c r="Y286" t="n">
         <v>0</v>
       </c>
-      <c r="Z286" t="n">
-        <v>133974.3637</v>
-      </c>
-      <c r="AA286" t="n">
-        <v>0.032142309239764</v>
-      </c>
+      <c r="Z286" t="inlineStr"/>
+      <c r="AA286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -23696,12 +23708,8 @@
       <c r="Y291" t="n">
         <v>0</v>
       </c>
-      <c r="Z291" t="n">
-        <v>160583.7741</v>
-      </c>
-      <c r="AA291" t="n">
-        <v>-1.518675665695694</v>
-      </c>
+      <c r="Z291" t="inlineStr"/>
+      <c r="AA291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -23858,12 +23866,8 @@
       <c r="Y293" t="n">
         <v>0</v>
       </c>
-      <c r="Z293" t="n">
-        <v>129943.0837999999</v>
-      </c>
-      <c r="AA293" t="n">
-        <v>-1.142676362869783</v>
-      </c>
+      <c r="Z293" t="inlineStr"/>
+      <c r="AA293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -24257,12 +24261,8 @@
       <c r="Y298" t="n">
         <v>0</v>
       </c>
-      <c r="Z298" t="n">
-        <v>162214.636</v>
-      </c>
-      <c r="AA298" t="n">
-        <v>0.03127838906373458</v>
-      </c>
+      <c r="Z298" t="inlineStr"/>
+      <c r="AA298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -24340,8 +24340,12 @@
       <c r="Y299" t="n">
         <v>0</v>
       </c>
-      <c r="Z299" t="inlineStr"/>
-      <c r="AA299" t="inlineStr"/>
+      <c r="Z299" t="n">
+        <v>120550.8178</v>
+      </c>
+      <c r="AA299" t="n">
+        <v>-2.835114417470524</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -24419,8 +24423,12 @@
       <c r="Y300" t="n">
         <v>0</v>
       </c>
-      <c r="Z300" t="inlineStr"/>
-      <c r="AA300" t="inlineStr"/>
+      <c r="Z300" t="n">
+        <v>82195.53529999983</v>
+      </c>
+      <c r="AA300" t="n">
+        <v>0.5706306220868651</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -24498,8 +24506,12 @@
       <c r="Y301" t="n">
         <v>0</v>
       </c>
-      <c r="Z301" t="inlineStr"/>
-      <c r="AA301" t="inlineStr"/>
+      <c r="Z301" t="n">
+        <v>82667.25999999983</v>
+      </c>
+      <c r="AA301" t="n">
+        <v>1.936329660763347e-13</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -24577,12 +24589,8 @@
       <c r="Y302" t="n">
         <v>0</v>
       </c>
-      <c r="Z302" t="n">
-        <v>208321.5222</v>
-      </c>
-      <c r="AA302" t="n">
-        <v>-1.072108639302411</v>
-      </c>
+      <c r="Z302" t="inlineStr"/>
+      <c r="AA302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -24660,12 +24668,8 @@
       <c r="Y303" t="n">
         <v>0</v>
       </c>
-      <c r="Z303" t="n">
-        <v>67716.94000000013</v>
-      </c>
-      <c r="AA303" t="n">
-        <v>-1.934039504078325e-13</v>
-      </c>
+      <c r="Z303" t="inlineStr"/>
+      <c r="AA303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -24743,8 +24747,12 @@
       <c r="Y304" t="n">
         <v>0</v>
       </c>
-      <c r="Z304" t="inlineStr"/>
-      <c r="AA304" t="inlineStr"/>
+      <c r="Z304" t="n">
+        <v>142352.3377000001</v>
+      </c>
+      <c r="AA304" t="n">
+        <v>3.417192407297867</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -25059,12 +25067,8 @@
       <c r="Y308" t="n">
         <v>0</v>
       </c>
-      <c r="Z308" t="n">
-        <v>145411.1372000001</v>
-      </c>
-      <c r="AA308" t="n">
-        <v>-3.549987990118438</v>
-      </c>
+      <c r="Z308" t="inlineStr"/>
+      <c r="AA308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -25379,12 +25383,8 @@
       <c r="Y312" t="n">
         <v>0</v>
       </c>
-      <c r="Z312" t="n">
-        <v>67716.94000000013</v>
-      </c>
-      <c r="AA312" t="n">
-        <v>-1.934039504078325e-13</v>
-      </c>
+      <c r="Z312" t="inlineStr"/>
+      <c r="AA312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -25620,12 +25620,8 @@
       <c r="Y315" t="n">
         <v>0</v>
       </c>
-      <c r="Z315" t="n">
-        <v>137763.3283</v>
-      </c>
-      <c r="AA315" t="n">
-        <v>0.3226208063398218</v>
-      </c>
+      <c r="Z315" t="inlineStr"/>
+      <c r="AA315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -25782,8 +25778,12 @@
       <c r="Y317" t="n">
         <v>0</v>
       </c>
-      <c r="Z317" t="inlineStr"/>
-      <c r="AA317" t="inlineStr"/>
+      <c r="Z317" t="n">
+        <v>129668.9235</v>
+      </c>
+      <c r="AA317" t="n">
+        <v>-4.135945558139841</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -25861,12 +25861,8 @@
       <c r="Y318" t="n">
         <v>0</v>
       </c>
-      <c r="Z318" t="n">
-        <v>76393.42999999989</v>
-      </c>
-      <c r="AA318" t="n">
-        <v>1.333405328161963e-13</v>
-      </c>
+      <c r="Z318" t="inlineStr"/>
+      <c r="AA318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -25944,8 +25940,12 @@
       <c r="Y319" t="n">
         <v>0</v>
       </c>
-      <c r="Z319" t="inlineStr"/>
-      <c r="AA319" t="inlineStr"/>
+      <c r="Z319" t="n">
+        <v>76393.42999999989</v>
+      </c>
+      <c r="AA319" t="n">
+        <v>1.333405328161963e-13</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -26023,8 +26023,12 @@
       <c r="Y320" t="n">
         <v>0</v>
       </c>
-      <c r="Z320" t="inlineStr"/>
-      <c r="AA320" t="inlineStr"/>
+      <c r="Z320" t="n">
+        <v>82667.25999999983</v>
+      </c>
+      <c r="AA320" t="n">
+        <v>1.936329660763347e-13</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -26182,10 +26186,10 @@
         <v>0</v>
       </c>
       <c r="Z322" t="n">
-        <v>92766.27279999996</v>
+        <v>92529.06459999995</v>
       </c>
       <c r="AA322" t="n">
-        <v>0.1048926770940271</v>
+        <v>0.3603296789444903</v>
       </c>
     </row>
     <row r="323">
@@ -26580,8 +26584,12 @@
       <c r="Y327" t="n">
         <v>0</v>
       </c>
-      <c r="Z327" t="inlineStr"/>
-      <c r="AA327" t="inlineStr"/>
+      <c r="Z327" t="n">
+        <v>15698.54590000003</v>
+      </c>
+      <c r="AA327" t="n">
+        <v>-2.107285671915387</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -26817,8 +26825,12 @@
       <c r="Y330" t="n">
         <v>0</v>
       </c>
-      <c r="Z330" t="inlineStr"/>
-      <c r="AA330" t="inlineStr"/>
+      <c r="Z330" t="n">
+        <v>67716.94000000013</v>
+      </c>
+      <c r="AA330" t="n">
+        <v>-1.934039504078325e-13</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -26976,10 +26988,10 @@
         <v>0</v>
       </c>
       <c r="Z332" t="n">
-        <v>115005.6822999999</v>
+        <v>113712.0373999999</v>
       </c>
       <c r="AA332" t="n">
-        <v>-2.270554054031158</v>
+        <v>-1.12016062975624</v>
       </c>
     </row>
     <row r="333">
@@ -27138,10 +27150,10 @@
         <v>0</v>
       </c>
       <c r="Z334" t="n">
-        <v>144050.9167000002</v>
+        <v>145898.4743000002</v>
       </c>
       <c r="AA334" t="n">
-        <v>2.264745377704671</v>
+        <v>1.011219772994954</v>
       </c>
     </row>
     <row r="335">
@@ -27220,12 +27232,8 @@
       <c r="Y335" t="n">
         <v>0</v>
       </c>
-      <c r="Z335" t="n">
-        <v>73058.59999999987</v>
-      </c>
-      <c r="AA335" t="n">
-        <v>1.792632722982669e-13</v>
-      </c>
+      <c r="Z335" t="inlineStr"/>
+      <c r="AA335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -27382,12 +27390,8 @@
       <c r="Y337" t="n">
         <v>0</v>
       </c>
-      <c r="Z337" t="n">
-        <v>92972.93170000003</v>
-      </c>
-      <c r="AA337" t="n">
-        <v>0.2836825296449751</v>
-      </c>
+      <c r="Z337" t="inlineStr"/>
+      <c r="AA337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -27466,10 +27470,10 @@
         <v>0</v>
       </c>
       <c r="Z338" t="n">
-        <v>126881.4460000001</v>
+        <v>126818.9634999999</v>
       </c>
       <c r="AA338" t="n">
-        <v>-0.08380661201881121</v>
+        <v>-0.03452055291559818</v>
       </c>
     </row>
     <row r="339">
@@ -28022,12 +28026,8 @@
       <c r="Y345" t="n">
         <v>0</v>
       </c>
-      <c r="Z345" t="n">
-        <v>79058.57000000011</v>
-      </c>
-      <c r="AA345" t="n">
-        <v>-1.288454959387299e-13</v>
-      </c>
+      <c r="Z345" t="inlineStr"/>
+      <c r="AA345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -28105,8 +28105,12 @@
       <c r="Y346" t="n">
         <v>0</v>
       </c>
-      <c r="Z346" t="inlineStr"/>
-      <c r="AA346" t="inlineStr"/>
+      <c r="Z346" t="n">
+        <v>100557.8332</v>
+      </c>
+      <c r="AA346" t="n">
+        <v>-0.9768467231623912</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -28264,10 +28268,10 @@
         <v>0</v>
       </c>
       <c r="Z348" t="n">
-        <v>163505.2533999999</v>
+        <v>163003.5838</v>
       </c>
       <c r="AA348" t="n">
-        <v>-1.60887569445254</v>
+        <v>-1.297117613497331</v>
       </c>
     </row>
     <row r="349">
@@ -29294,12 +29298,8 @@
       <c r="Y361" t="n">
         <v>0</v>
       </c>
-      <c r="Z361" t="n">
-        <v>115866.0045999999</v>
-      </c>
-      <c r="AA361" t="n">
-        <v>0.03371327641555857</v>
-      </c>
+      <c r="Z361" t="inlineStr"/>
+      <c r="AA361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -29535,8 +29535,12 @@
       <c r="Y364" t="n">
         <v>0</v>
       </c>
-      <c r="Z364" t="inlineStr"/>
-      <c r="AA364" t="inlineStr"/>
+      <c r="Z364" t="n">
+        <v>168112.9885</v>
+      </c>
+      <c r="AA364" t="n">
+        <v>1.351822462021346</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -29693,12 +29697,8 @@
       <c r="Y366" t="n">
         <v>0</v>
       </c>
-      <c r="Z366" t="n">
-        <v>75366.1464999999</v>
-      </c>
-      <c r="AA366" t="n">
-        <v>-0.1788430659455533</v>
-      </c>
+      <c r="Z366" t="inlineStr"/>
+      <c r="AA366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -29776,8 +29776,12 @@
       <c r="Y367" t="n">
         <v>0</v>
       </c>
-      <c r="Z367" t="inlineStr"/>
-      <c r="AA367" t="inlineStr"/>
+      <c r="Z367" t="n">
+        <v>162447.3230000004</v>
+      </c>
+      <c r="AA367" t="n">
+        <v>1.505368970484442</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -29935,10 +29939,10 @@
         <v>0</v>
       </c>
       <c r="Z369" t="n">
-        <v>211413.1088</v>
+        <v>217088.6654000001</v>
       </c>
       <c r="AA369" t="n">
-        <v>1.253618837474044</v>
+        <v>-1.397307959422381</v>
       </c>
     </row>
     <row r="370">
@@ -30096,12 +30100,8 @@
       <c r="Y371" t="n">
         <v>0</v>
       </c>
-      <c r="Z371" t="n">
-        <v>144355.2436000002</v>
-      </c>
-      <c r="AA371" t="n">
-        <v>2.05826653160431</v>
-      </c>
+      <c r="Z371" t="inlineStr"/>
+      <c r="AA371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -30258,8 +30258,12 @@
       <c r="Y373" t="n">
         <v>0</v>
       </c>
-      <c r="Z373" t="inlineStr"/>
-      <c r="AA373" t="inlineStr"/>
+      <c r="Z373" t="n">
+        <v>100443.1349</v>
+      </c>
+      <c r="AA373" t="n">
+        <v>-1.511708045916178</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -30337,8 +30341,12 @@
       <c r="Y374" t="n">
         <v>0</v>
       </c>
-      <c r="Z374" t="inlineStr"/>
-      <c r="AA374" t="inlineStr"/>
+      <c r="Z374" t="n">
+        <v>143132.9625</v>
+      </c>
+      <c r="AA374" t="n">
+        <v>-0.04004349586481788</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -30969,8 +30977,12 @@
       <c r="Y382" t="n">
         <v>0</v>
       </c>
-      <c r="Z382" t="inlineStr"/>
-      <c r="AA382" t="inlineStr"/>
+      <c r="Z382" t="n">
+        <v>249042.2055999998</v>
+      </c>
+      <c r="AA382" t="n">
+        <v>4.593684674270496</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -31522,12 +31534,8 @@
       <c r="Y389" t="n">
         <v>0</v>
       </c>
-      <c r="Z389" t="n">
-        <v>103127.5720000001</v>
-      </c>
-      <c r="AA389" t="n">
-        <v>1.024632710972441</v>
-      </c>
+      <c r="Z389" t="inlineStr"/>
+      <c r="AA389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -31842,12 +31850,8 @@
       <c r="Y393" t="n">
         <v>0</v>
       </c>
-      <c r="Z393" t="n">
-        <v>132428.0214999999</v>
-      </c>
-      <c r="AA393" t="n">
-        <v>3.03153341852167</v>
-      </c>
+      <c r="Z393" t="inlineStr"/>
+      <c r="AA393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -31925,12 +31929,8 @@
       <c r="Y394" t="n">
         <v>0</v>
       </c>
-      <c r="Z394" t="n">
-        <v>153500.6567999999</v>
-      </c>
-      <c r="AA394" t="n">
-        <v>-0.9483227688789264</v>
-      </c>
+      <c r="Z394" t="inlineStr"/>
+      <c r="AA394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -32245,8 +32245,12 @@
       <c r="Y398" t="n">
         <v>0</v>
       </c>
-      <c r="Z398" t="inlineStr"/>
-      <c r="AA398" t="inlineStr"/>
+      <c r="Z398" t="n">
+        <v>95948.00209999991</v>
+      </c>
+      <c r="AA398" t="n">
+        <v>2.435560014768784</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -32561,12 +32565,8 @@
       <c r="Y402" t="n">
         <v>0</v>
       </c>
-      <c r="Z402" t="n">
-        <v>128198.7675000001</v>
-      </c>
-      <c r="AA402" t="n">
-        <v>-0.8968156438475613</v>
-      </c>
+      <c r="Z402" t="inlineStr"/>
+      <c r="AA402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -32960,12 +32960,8 @@
       <c r="Y407" t="n">
         <v>0</v>
       </c>
-      <c r="Z407" t="n">
-        <v>172980.0978000001</v>
-      </c>
-      <c r="AA407" t="n">
-        <v>-3.163264809538187</v>
-      </c>
+      <c r="Z407" t="inlineStr"/>
+      <c r="AA407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -33596,12 +33592,8 @@
       <c r="Y415" t="n">
         <v>0</v>
       </c>
-      <c r="Z415" t="n">
-        <v>113133.5756999999</v>
-      </c>
-      <c r="AA415" t="n">
-        <v>-1.979009645919579</v>
-      </c>
+      <c r="Z415" t="inlineStr"/>
+      <c r="AA415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -33759,10 +33751,10 @@
         <v>0</v>
       </c>
       <c r="Z417" t="n">
-        <v>135477.483</v>
+        <v>138881.0577</v>
       </c>
       <c r="AA417" t="n">
-        <v>-3.869209919985212</v>
+        <v>-6.478696066053097</v>
       </c>
     </row>
     <row r="418">
@@ -33920,12 +33912,8 @@
       <c r="Y419" t="n">
         <v>0</v>
       </c>
-      <c r="Z419" t="n">
-        <v>130068.0596000001</v>
-      </c>
-      <c r="AA419" t="n">
-        <v>1.329990524290912</v>
-      </c>
+      <c r="Z419" t="inlineStr"/>
+      <c r="AA419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -34003,12 +33991,8 @@
       <c r="Y420" t="n">
         <v>0</v>
       </c>
-      <c r="Z420" t="n">
-        <v>178606.7177</v>
-      </c>
-      <c r="AA420" t="n">
-        <v>3.885480951932785</v>
-      </c>
+      <c r="Z420" t="inlineStr"/>
+      <c r="AA420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -34564,8 +34548,12 @@
       <c r="Y427" t="n">
         <v>0</v>
       </c>
-      <c r="Z427" t="inlineStr"/>
-      <c r="AA427" t="inlineStr"/>
+      <c r="Z427" t="n">
+        <v>98595.95810000018</v>
+      </c>
+      <c r="AA427" t="n">
+        <v>1.02643796612819</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -34643,8 +34631,12 @@
       <c r="Y428" t="n">
         <v>0</v>
       </c>
-      <c r="Z428" t="inlineStr"/>
-      <c r="AA428" t="inlineStr"/>
+      <c r="Z428" t="n">
+        <v>82667.25999999983</v>
+      </c>
+      <c r="AA428" t="n">
+        <v>1.936329660763347e-13</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -34801,12 +34793,8 @@
       <c r="Y430" t="n">
         <v>0</v>
       </c>
-      <c r="Z430" t="n">
-        <v>232958.5877000001</v>
-      </c>
-      <c r="AA430" t="n">
-        <v>9.789222922149065</v>
-      </c>
+      <c r="Z430" t="inlineStr"/>
+      <c r="AA430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -34884,12 +34872,8 @@
       <c r="Y431" t="n">
         <v>0</v>
       </c>
-      <c r="Z431" t="n">
-        <v>22661.38150000004</v>
-      </c>
-      <c r="AA431" t="n">
-        <v>-0.3946051600391728</v>
-      </c>
+      <c r="Z431" t="inlineStr"/>
+      <c r="AA431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -35125,8 +35109,12 @@
       <c r="Y434" t="n">
         <v>0</v>
       </c>
-      <c r="Z434" t="inlineStr"/>
-      <c r="AA434" t="inlineStr"/>
+      <c r="Z434" t="n">
+        <v>183139.2645999999</v>
+      </c>
+      <c r="AA434" t="n">
+        <v>-0.5012927369551712</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -35204,8 +35192,12 @@
       <c r="Y435" t="n">
         <v>0</v>
       </c>
-      <c r="Z435" t="inlineStr"/>
-      <c r="AA435" t="inlineStr"/>
+      <c r="Z435" t="n">
+        <v>194634.9337</v>
+      </c>
+      <c r="AA435" t="n">
+        <v>7.059274557363279</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -35441,8 +35433,12 @@
       <c r="Y438" t="n">
         <v>0</v>
       </c>
-      <c r="Z438" t="inlineStr"/>
-      <c r="AA438" t="inlineStr"/>
+      <c r="Z438" t="n">
+        <v>83489.88869999984</v>
+      </c>
+      <c r="AA438" t="n">
+        <v>-0.995108220594031</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -35520,8 +35516,12 @@
       <c r="Y439" t="n">
         <v>0</v>
       </c>
-      <c r="Z439" t="inlineStr"/>
-      <c r="AA439" t="inlineStr"/>
+      <c r="Z439" t="n">
+        <v>79058.57000000011</v>
+      </c>
+      <c r="AA439" t="n">
+        <v>-1.288454959387299e-13</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -35678,12 +35678,8 @@
       <c r="Y441" t="n">
         <v>0</v>
       </c>
-      <c r="Z441" t="n">
-        <v>156129.6451999998</v>
-      </c>
-      <c r="AA441" t="n">
-        <v>1.313030053357445</v>
-      </c>
+      <c r="Z441" t="inlineStr"/>
+      <c r="AA441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -35761,8 +35757,12 @@
       <c r="Y442" t="n">
         <v>0</v>
       </c>
-      <c r="Z442" t="inlineStr"/>
-      <c r="AA442" t="inlineStr"/>
+      <c r="Z442" t="n">
+        <v>103866.4206</v>
+      </c>
+      <c r="AA442" t="n">
+        <v>0.8844361635887553</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -35998,8 +35998,12 @@
       <c r="Y445" t="n">
         <v>0</v>
       </c>
-      <c r="Z445" t="inlineStr"/>
-      <c r="AA445" t="inlineStr"/>
+      <c r="Z445" t="n">
+        <v>193746.1245999999</v>
+      </c>
+      <c r="AA445" t="n">
+        <v>-0.9912059529446656</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -36393,8 +36397,12 @@
       <c r="Y450" t="n">
         <v>0</v>
       </c>
-      <c r="Z450" t="inlineStr"/>
-      <c r="AA450" t="inlineStr"/>
+      <c r="Z450" t="n">
+        <v>149763.0388</v>
+      </c>
+      <c r="AA450" t="n">
+        <v>-3.685667381245051</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -36630,12 +36638,8 @@
       <c r="Y453" t="n">
         <v>0</v>
       </c>
-      <c r="Z453" t="n">
-        <v>74192.44219999989</v>
-      </c>
-      <c r="AA453" t="n">
-        <v>-1.551962671061152</v>
-      </c>
+      <c r="Z453" t="inlineStr"/>
+      <c r="AA453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -36792,8 +36796,12 @@
       <c r="Y455" t="n">
         <v>0</v>
       </c>
-      <c r="Z455" t="inlineStr"/>
-      <c r="AA455" t="inlineStr"/>
+      <c r="Z455" t="n">
+        <v>67716.94000000013</v>
+      </c>
+      <c r="AA455" t="n">
+        <v>-1.934039504078325e-13</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -37108,8 +37116,12 @@
       <c r="Y459" t="n">
         <v>0</v>
       </c>
-      <c r="Z459" t="inlineStr"/>
-      <c r="AA459" t="inlineStr"/>
+      <c r="Z459" t="n">
+        <v>104001.7388</v>
+      </c>
+      <c r="AA459" t="n">
+        <v>0.6577599559080793</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -37266,8 +37278,12 @@
       <c r="Y461" t="n">
         <v>0</v>
       </c>
-      <c r="Z461" t="inlineStr"/>
-      <c r="AA461" t="inlineStr"/>
+      <c r="Z461" t="n">
+        <v>82667.25999999983</v>
+      </c>
+      <c r="AA461" t="n">
+        <v>1.936329660763347e-13</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -37582,8 +37598,12 @@
       <c r="Y465" t="n">
         <v>0</v>
       </c>
-      <c r="Z465" t="inlineStr"/>
-      <c r="AA465" t="inlineStr"/>
+      <c r="Z465" t="n">
+        <v>82667.25999999983</v>
+      </c>
+      <c r="AA465" t="n">
+        <v>1.936329660763347e-13</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -37740,12 +37760,8 @@
       <c r="Y467" t="n">
         <v>0</v>
       </c>
-      <c r="Z467" t="n">
-        <v>153100.703</v>
-      </c>
-      <c r="AA467" t="n">
-        <v>0.02795874092485925</v>
-      </c>
+      <c r="Z467" t="inlineStr"/>
+      <c r="AA467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -37981,12 +37997,8 @@
       <c r="Y470" t="n">
         <v>0</v>
       </c>
-      <c r="Z470" t="n">
-        <v>145443.5476</v>
-      </c>
-      <c r="AA470" t="n">
-        <v>-1.035314120882914</v>
-      </c>
+      <c r="Z470" t="inlineStr"/>
+      <c r="AA470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -38143,12 +38155,8 @@
       <c r="Y472" t="n">
         <v>0</v>
       </c>
-      <c r="Z472" t="n">
-        <v>82667.25999999983</v>
-      </c>
-      <c r="AA472" t="n">
-        <v>1.936329660763347e-13</v>
-      </c>
+      <c r="Z472" t="inlineStr"/>
+      <c r="AA472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -38463,8 +38471,12 @@
       <c r="Y476" t="n">
         <v>0</v>
       </c>
-      <c r="Z476" t="inlineStr"/>
-      <c r="AA476" t="inlineStr"/>
+      <c r="Z476" t="n">
+        <v>82667.25999999983</v>
+      </c>
+      <c r="AA476" t="n">
+        <v>1.936329660763347e-13</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -38621,12 +38633,8 @@
       <c r="Y478" t="n">
         <v>0</v>
       </c>
-      <c r="Z478" t="n">
-        <v>246163.2852999998</v>
-      </c>
-      <c r="AA478" t="n">
-        <v>4.945011716637583</v>
-      </c>
+      <c r="Z478" t="inlineStr"/>
+      <c r="AA478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -38783,8 +38791,12 @@
       <c r="Y480" t="n">
         <v>0</v>
       </c>
-      <c r="Z480" t="inlineStr"/>
-      <c r="AA480" t="inlineStr"/>
+      <c r="Z480" t="n">
+        <v>67716.94000000013</v>
+      </c>
+      <c r="AA480" t="n">
+        <v>-1.934039504078325e-13</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -39179,10 +39191,10 @@
         <v>0</v>
       </c>
       <c r="Z485" t="n">
-        <v>161783.9642</v>
+        <v>162154.0479000002</v>
       </c>
       <c r="AA485" t="n">
-        <v>-0.06260668269232395</v>
+        <v>-0.2915016779157502</v>
       </c>
     </row>
     <row r="486">
@@ -39419,12 +39431,8 @@
       <c r="Y488" t="n">
         <v>0</v>
       </c>
-      <c r="Z488" t="n">
-        <v>82667.25999999983</v>
-      </c>
-      <c r="AA488" t="n">
-        <v>1.936329660763347e-13</v>
-      </c>
+      <c r="Z488" t="inlineStr"/>
+      <c r="AA488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -39897,12 +39905,8 @@
       <c r="Y494" t="n">
         <v>0</v>
       </c>
-      <c r="Z494" t="n">
-        <v>82216.35039999984</v>
-      </c>
-      <c r="AA494" t="n">
-        <v>0.5454512463581824</v>
-      </c>
+      <c r="Z494" t="inlineStr"/>
+      <c r="AA494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -40217,12 +40221,8 @@
       <c r="Y498" t="n">
         <v>0</v>
       </c>
-      <c r="Z498" t="n">
-        <v>95178.58069999995</v>
-      </c>
-      <c r="AA498" t="n">
-        <v>0.1309599794929139</v>
-      </c>
+      <c r="Z498" t="inlineStr"/>
+      <c r="AA498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -40300,12 +40300,8 @@
       <c r="Y499" t="n">
         <v>0</v>
       </c>
-      <c r="Z499" t="n">
-        <v>73058.59999999987</v>
-      </c>
-      <c r="AA499" t="n">
-        <v>1.792632722982669e-13</v>
-      </c>
+      <c r="Z499" t="inlineStr"/>
+      <c r="AA499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -40383,12 +40379,8 @@
       <c r="Y500" t="n">
         <v>0</v>
       </c>
-      <c r="Z500" t="n">
-        <v>67716.94000000013</v>
-      </c>
-      <c r="AA500" t="n">
-        <v>-1.934039504078325e-13</v>
-      </c>
+      <c r="Z500" t="inlineStr"/>
+      <c r="AA500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -40545,12 +40537,8 @@
       <c r="Y502" t="n">
         <v>0</v>
       </c>
-      <c r="Z502" t="n">
-        <v>163657.361</v>
-      </c>
-      <c r="AA502" t="n">
-        <v>-3.058642295417326</v>
-      </c>
+      <c r="Z502" t="inlineStr"/>
+      <c r="AA502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -40944,8 +40932,12 @@
       <c r="Y507" t="n">
         <v>0</v>
       </c>
-      <c r="Z507" t="inlineStr"/>
-      <c r="AA507" t="inlineStr"/>
+      <c r="Z507" t="n">
+        <v>98856.26920000017</v>
+      </c>
+      <c r="AA507" t="n">
+        <v>0.7651299236846679</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -41023,12 +41015,8 @@
       <c r="Y508" t="n">
         <v>0</v>
       </c>
-      <c r="Z508" t="n">
-        <v>162214.636</v>
-      </c>
-      <c r="AA508" t="n">
-        <v>-0.4133947306047269</v>
-      </c>
+      <c r="Z508" t="inlineStr"/>
+      <c r="AA508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -41422,8 +41410,12 @@
       <c r="Y513" t="n">
         <v>0</v>
       </c>
-      <c r="Z513" t="inlineStr"/>
-      <c r="AA513" t="inlineStr"/>
+      <c r="Z513" t="n">
+        <v>41613.68789999998</v>
+      </c>
+      <c r="AA513" t="n">
+        <v>0.2744715686411398</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -41817,8 +41809,12 @@
       <c r="Y518" t="n">
         <v>0</v>
       </c>
-      <c r="Z518" t="inlineStr"/>
-      <c r="AA518" t="inlineStr"/>
+      <c r="Z518" t="n">
+        <v>143628.1697</v>
+      </c>
+      <c r="AA518" t="n">
+        <v>9.662636183911937</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -41979,12 +41975,8 @@
       <c r="Y520" t="n">
         <v>0</v>
       </c>
-      <c r="Z520" t="n">
-        <v>67716.94000000013</v>
-      </c>
-      <c r="AA520" t="n">
-        <v>-1.934039504078325e-13</v>
-      </c>
+      <c r="Z520" t="inlineStr"/>
+      <c r="AA520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -42220,8 +42212,12 @@
       <c r="Y523" t="n">
         <v>0</v>
       </c>
-      <c r="Z523" t="inlineStr"/>
-      <c r="AA523" t="inlineStr"/>
+      <c r="Z523" t="n">
+        <v>83895.30700000002</v>
+      </c>
+      <c r="AA523" t="n">
+        <v>-7.464632999277697</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -42536,8 +42532,12 @@
       <c r="Y527" t="n">
         <v>0</v>
       </c>
-      <c r="Z527" t="inlineStr"/>
-      <c r="AA527" t="inlineStr"/>
+      <c r="Z527" t="n">
+        <v>167435.0704000001</v>
+      </c>
+      <c r="AA527" t="n">
+        <v>-2.020273165739556</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -42615,8 +42615,12 @@
       <c r="Y528" t="n">
         <v>0</v>
       </c>
-      <c r="Z528" t="inlineStr"/>
-      <c r="AA528" t="inlineStr"/>
+      <c r="Z528" t="n">
+        <v>100008.7972</v>
+      </c>
+      <c r="AA528" t="n">
+        <v>-1.676712153842828</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -42694,12 +42698,8 @@
       <c r="Y529" t="n">
         <v>0</v>
       </c>
-      <c r="Z529" t="n">
-        <v>82667.25999999983</v>
-      </c>
-      <c r="AA529" t="n">
-        <v>1.936329660763347e-13</v>
-      </c>
+      <c r="Z529" t="inlineStr"/>
+      <c r="AA529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -43409,12 +43409,8 @@
       <c r="Y538" t="n">
         <v>0</v>
       </c>
-      <c r="Z538" t="n">
-        <v>162920.8027999999</v>
-      </c>
-      <c r="AA538" t="n">
-        <v>-8.535881884336673</v>
-      </c>
+      <c r="Z538" t="inlineStr"/>
+      <c r="AA538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="n">
@@ -43571,8 +43567,12 @@
       <c r="Y540" t="n">
         <v>0</v>
       </c>
-      <c r="Z540" t="inlineStr"/>
-      <c r="AA540" t="inlineStr"/>
+      <c r="Z540" t="n">
+        <v>51349.62710000005</v>
+      </c>
+      <c r="AA540" t="n">
+        <v>-0.8920158764122802</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
@@ -43887,8 +43887,12 @@
       <c r="Y544" t="n">
         <v>0</v>
       </c>
-      <c r="Z544" t="inlineStr"/>
-      <c r="AA544" t="inlineStr"/>
+      <c r="Z544" t="n">
+        <v>150024.0495999997</v>
+      </c>
+      <c r="AA544" t="n">
+        <v>1.340884938246843</v>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="n">
@@ -44282,8 +44286,12 @@
       <c r="Y549" t="n">
         <v>0</v>
       </c>
-      <c r="Z549" t="inlineStr"/>
-      <c r="AA549" t="inlineStr"/>
+      <c r="Z549" t="n">
+        <v>102974.5253999999</v>
+      </c>
+      <c r="AA549" t="n">
+        <v>0.5548621001751646</v>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="n">
@@ -44361,8 +44369,12 @@
       <c r="Y550" t="n">
         <v>0</v>
       </c>
-      <c r="Z550" t="inlineStr"/>
-      <c r="AA550" t="inlineStr"/>
+      <c r="Z550" t="n">
+        <v>129525.7973</v>
+      </c>
+      <c r="AA550" t="n">
+        <v>-0.1098185389798953</v>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="n">
@@ -44440,8 +44452,12 @@
       <c r="Y551" t="n">
         <v>0</v>
       </c>
-      <c r="Z551" t="inlineStr"/>
-      <c r="AA551" t="inlineStr"/>
+      <c r="Z551" t="n">
+        <v>139554.4251</v>
+      </c>
+      <c r="AA551" t="n">
+        <v>-2.438430876511156</v>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
@@ -44520,10 +44536,10 @@
         <v>0</v>
       </c>
       <c r="Z552" t="n">
-        <v>124697.3552</v>
+        <v>124778.8846999999</v>
       </c>
       <c r="AA552" t="n">
-        <v>1.324413356447241</v>
+        <v>1.259897383126546</v>
       </c>
     </row>
     <row r="553">
@@ -44602,12 +44618,8 @@
       <c r="Y553" t="n">
         <v>0</v>
       </c>
-      <c r="Z553" t="n">
-        <v>135076.1099000002</v>
-      </c>
-      <c r="AA553" t="n">
-        <v>-0.7854597193133293</v>
-      </c>
+      <c r="Z553" t="inlineStr"/>
+      <c r="AA553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" t="n">
@@ -44764,12 +44776,8 @@
       <c r="Y555" t="n">
         <v>0</v>
       </c>
-      <c r="Z555" t="n">
-        <v>155077.8789999999</v>
-      </c>
-      <c r="AA555" t="n">
-        <v>0.07453981982248409</v>
-      </c>
+      <c r="Z555" t="inlineStr"/>
+      <c r="AA555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" t="n">
@@ -44847,8 +44855,12 @@
       <c r="Y556" t="n">
         <v>0</v>
       </c>
-      <c r="Z556" t="inlineStr"/>
-      <c r="AA556" t="inlineStr"/>
+      <c r="Z556" t="n">
+        <v>51671.44149999999</v>
+      </c>
+      <c r="AA556" t="n">
+        <v>2.017968686445964</v>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
@@ -45005,8 +45017,12 @@
       <c r="Y558" t="n">
         <v>0</v>
       </c>
-      <c r="Z558" t="inlineStr"/>
-      <c r="AA558" t="inlineStr"/>
+      <c r="Z558" t="n">
+        <v>114870.7674</v>
+      </c>
+      <c r="AA558" t="n">
+        <v>2.74029121836301</v>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="n">
@@ -45321,8 +45337,12 @@
       <c r="Y562" t="n">
         <v>0</v>
       </c>
-      <c r="Z562" t="inlineStr"/>
-      <c r="AA562" t="inlineStr"/>
+      <c r="Z562" t="n">
+        <v>128944.8385</v>
+      </c>
+      <c r="AA562" t="n">
+        <v>-0.3516522574500149</v>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
@@ -45480,10 +45500,10 @@
         <v>0</v>
       </c>
       <c r="Z564" t="n">
-        <v>140309.7372000001</v>
+        <v>139990.7468</v>
       </c>
       <c r="AA564" t="n">
-        <v>-0.9850339481933543</v>
+        <v>-0.7554471995043853</v>
       </c>
     </row>
     <row r="565">
@@ -45720,8 +45740,12 @@
       <c r="Y567" t="n">
         <v>0</v>
       </c>
-      <c r="Z567" t="inlineStr"/>
-      <c r="AA567" t="inlineStr"/>
+      <c r="Z567" t="n">
+        <v>151759.6994</v>
+      </c>
+      <c r="AA567" t="n">
+        <v>1.017236836166483</v>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
@@ -46273,12 +46297,8 @@
       <c r="Y574" t="n">
         <v>0</v>
       </c>
-      <c r="Z574" t="n">
-        <v>168354.2780999999</v>
-      </c>
-      <c r="AA574" t="n">
-        <v>4.994033370597439</v>
-      </c>
+      <c r="Z574" t="inlineStr"/>
+      <c r="AA574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" t="n">
@@ -46356,8 +46376,12 @@
       <c r="Y575" t="n">
         <v>0</v>
       </c>
-      <c r="Z575" t="inlineStr"/>
-      <c r="AA575" t="inlineStr"/>
+      <c r="Z575" t="n">
+        <v>135612.3181000001</v>
+      </c>
+      <c r="AA575" t="n">
+        <v>-5.943721728935158</v>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="n">
@@ -46672,12 +46696,8 @@
       <c r="Y579" t="n">
         <v>0</v>
       </c>
-      <c r="Z579" t="n">
-        <v>49343.60550000003</v>
-      </c>
-      <c r="AA579" t="n">
-        <v>0.08187766735968528</v>
-      </c>
+      <c r="Z579" t="inlineStr"/>
+      <c r="AA579" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" t="n">
@@ -46755,12 +46775,8 @@
       <c r="Y580" t="n">
         <v>0</v>
       </c>
-      <c r="Z580" t="n">
-        <v>194312.2238000001</v>
-      </c>
-      <c r="AA580" t="n">
-        <v>-0.6882924396865958</v>
-      </c>
+      <c r="Z580" t="inlineStr"/>
+      <c r="AA580" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" t="n">
@@ -46917,8 +46933,12 @@
       <c r="Y582" t="n">
         <v>0</v>
       </c>
-      <c r="Z582" t="inlineStr"/>
-      <c r="AA582" t="inlineStr"/>
+      <c r="Z582" t="n">
+        <v>22572.31000000004</v>
+      </c>
+      <c r="AA582" t="n">
+        <v>-1.772869807211085e-13</v>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="n">
@@ -47474,12 +47494,8 @@
       <c r="Y589" t="n">
         <v>0</v>
       </c>
-      <c r="Z589" t="n">
-        <v>98617.51770000005</v>
-      </c>
-      <c r="AA589" t="n">
-        <v>2.418707800000958</v>
-      </c>
+      <c r="Z589" t="inlineStr"/>
+      <c r="AA589" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" t="n">
@@ -47557,8 +47573,12 @@
       <c r="Y590" t="n">
         <v>0</v>
       </c>
-      <c r="Z590" t="inlineStr"/>
-      <c r="AA590" t="inlineStr"/>
+      <c r="Z590" t="n">
+        <v>135546.8269000002</v>
+      </c>
+      <c r="AA590" t="n">
+        <v>-0.1349226113643186</v>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="n">
@@ -47636,8 +47656,12 @@
       <c r="Y591" t="n">
         <v>0</v>
       </c>
-      <c r="Z591" t="inlineStr"/>
-      <c r="AA591" t="inlineStr"/>
+      <c r="Z591" t="n">
+        <v>67716.94000000013</v>
+      </c>
+      <c r="AA591" t="n">
+        <v>-1.934039504078325e-13</v>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="n">
@@ -48035,8 +48059,12 @@
       <c r="Y596" t="n">
         <v>0</v>
       </c>
-      <c r="Z596" t="inlineStr"/>
-      <c r="AA596" t="inlineStr"/>
+      <c r="Z596" t="n">
+        <v>101180.1113</v>
+      </c>
+      <c r="AA596" t="n">
+        <v>-0.1535672814354594</v>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="n">
@@ -48430,12 +48458,8 @@
       <c r="Y601" t="n">
         <v>0</v>
       </c>
-      <c r="Z601" t="n">
-        <v>96484.07849999996</v>
-      </c>
-      <c r="AA601" t="n">
-        <v>0.0002606640892279009</v>
-      </c>
+      <c r="Z601" t="inlineStr"/>
+      <c r="AA601" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" t="n">
@@ -48513,8 +48537,12 @@
       <c r="Y602" t="n">
         <v>0</v>
       </c>
-      <c r="Z602" t="inlineStr"/>
-      <c r="AA602" t="inlineStr"/>
+      <c r="Z602" t="n">
+        <v>125140.0620999998</v>
+      </c>
+      <c r="AA602" t="n">
+        <v>8.403635057836356</v>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="n">
@@ -48671,8 +48699,12 @@
       <c r="Y604" t="n">
         <v>0</v>
       </c>
-      <c r="Z604" t="inlineStr"/>
-      <c r="AA604" t="inlineStr"/>
+      <c r="Z604" t="n">
+        <v>62577.71999999998</v>
+      </c>
+      <c r="AA604" t="n">
+        <v>3.488122105207776e-14</v>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="n">
@@ -48987,8 +49019,12 @@
       <c r="Y608" t="n">
         <v>0</v>
       </c>
-      <c r="Z608" t="inlineStr"/>
-      <c r="AA608" t="inlineStr"/>
+      <c r="Z608" t="n">
+        <v>93044.37169999997</v>
+      </c>
+      <c r="AA608" t="n">
+        <v>-0.7664034993669658</v>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="n">
@@ -49382,12 +49418,8 @@
       <c r="Y613" t="n">
         <v>0</v>
       </c>
-      <c r="Z613" t="n">
-        <v>152583.8325</v>
-      </c>
-      <c r="AA613" t="n">
-        <v>3.734747816988794</v>
-      </c>
+      <c r="Z613" t="inlineStr"/>
+      <c r="AA613" t="inlineStr"/>
     </row>
     <row r="614">
       <c r="A614" t="n">
@@ -49781,8 +49813,12 @@
       <c r="Y618" t="n">
         <v>0</v>
       </c>
-      <c r="Z618" t="inlineStr"/>
-      <c r="AA618" t="inlineStr"/>
+      <c r="Z618" t="n">
+        <v>102378.8605</v>
+      </c>
+      <c r="AA618" t="n">
+        <v>6.315818491146273</v>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="n">
@@ -49860,8 +49896,12 @@
       <c r="Y619" t="n">
         <v>0</v>
       </c>
-      <c r="Z619" t="inlineStr"/>
-      <c r="AA619" t="inlineStr"/>
+      <c r="Z619" t="n">
+        <v>78067.83000000006</v>
+      </c>
+      <c r="AA619" t="n">
+        <v>-7.456036745669428e-14</v>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="n">
@@ -50019,10 +50059,10 @@
         <v>0</v>
       </c>
       <c r="Z621" t="n">
-        <v>92989.67669999998</v>
+        <v>92838.50149999998</v>
       </c>
       <c r="AA621" t="n">
-        <v>3.201949187873098</v>
+        <v>3.359315738768239</v>
       </c>
     </row>
     <row r="622">
@@ -50417,12 +50457,8 @@
       <c r="Y626" t="n">
         <v>0</v>
       </c>
-      <c r="Z626" t="n">
-        <v>134501.9321000002</v>
-      </c>
-      <c r="AA626" t="n">
-        <v>0.2820811846406455</v>
-      </c>
+      <c r="Z626" t="inlineStr"/>
+      <c r="AA626" t="inlineStr"/>
     </row>
     <row r="627">
       <c r="A627" t="n">
@@ -50658,8 +50694,12 @@
       <c r="Y629" t="n">
         <v>0</v>
       </c>
-      <c r="Z629" t="inlineStr"/>
-      <c r="AA629" t="inlineStr"/>
+      <c r="Z629" t="n">
+        <v>42456.26539999995</v>
+      </c>
+      <c r="AA629" t="n">
+        <v>-0.5382689983365598</v>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="n">
@@ -50895,12 +50935,8 @@
       <c r="Y632" t="n">
         <v>0</v>
       </c>
-      <c r="Z632" t="n">
-        <v>67716.94000000013</v>
-      </c>
-      <c r="AA632" t="n">
-        <v>-1.934039504078325e-13</v>
-      </c>
+      <c r="Z632" t="inlineStr"/>
+      <c r="AA632" t="inlineStr"/>
     </row>
     <row r="633">
       <c r="A633" t="n">
@@ -50978,8 +51014,12 @@
       <c r="Y633" t="n">
         <v>0</v>
       </c>
-      <c r="Z633" t="inlineStr"/>
-      <c r="AA633" t="inlineStr"/>
+      <c r="Z633" t="n">
+        <v>100044.6536</v>
+      </c>
+      <c r="AA633" t="n">
+        <v>-1.74487144883284</v>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="n">
@@ -51057,12 +51097,8 @@
       <c r="Y634" t="n">
         <v>0</v>
       </c>
-      <c r="Z634" t="n">
-        <v>142485.6579999999</v>
-      </c>
-      <c r="AA634" t="n">
-        <v>-4.481342740191534</v>
-      </c>
+      <c r="Z634" t="inlineStr"/>
+      <c r="AA634" t="inlineStr"/>
     </row>
     <row r="635">
       <c r="A635" t="n">
@@ -51298,12 +51334,8 @@
       <c r="Y637" t="n">
         <v>0</v>
       </c>
-      <c r="Z637" t="n">
-        <v>15193.64310000002</v>
-      </c>
-      <c r="AA637" t="n">
-        <v>1.176728960048135</v>
-      </c>
+      <c r="Z637" t="inlineStr"/>
+      <c r="AA637" t="inlineStr"/>
     </row>
     <row r="638">
       <c r="A638" t="n">
@@ -51776,8 +51808,12 @@
       <c r="Y643" t="n">
         <v>0</v>
       </c>
-      <c r="Z643" t="inlineStr"/>
-      <c r="AA643" t="inlineStr"/>
+      <c r="Z643" t="n">
+        <v>126708.7329999999</v>
+      </c>
+      <c r="AA643" t="n">
+        <v>-0.04798577095115763</v>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="n">
@@ -51934,8 +51970,12 @@
       <c r="Y645" t="n">
         <v>0</v>
       </c>
-      <c r="Z645" t="inlineStr"/>
-      <c r="AA645" t="inlineStr"/>
+      <c r="Z645" t="n">
+        <v>67716.94000000013</v>
+      </c>
+      <c r="AA645" t="n">
+        <v>-1.934039504078325e-13</v>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="n">
@@ -52250,12 +52290,8 @@
       <c r="Y649" t="n">
         <v>0</v>
       </c>
-      <c r="Z649" t="n">
-        <v>147899.6004</v>
-      </c>
-      <c r="AA649" t="n">
-        <v>2.021852829403222</v>
-      </c>
+      <c r="Z649" t="inlineStr"/>
+      <c r="AA649" t="inlineStr"/>
     </row>
     <row r="650">
       <c r="A650" t="n">
@@ -52333,12 +52369,8 @@
       <c r="Y650" t="n">
         <v>0</v>
       </c>
-      <c r="Z650" t="n">
-        <v>177451.8601</v>
-      </c>
-      <c r="AA650" t="n">
-        <v>0.002073702517238494</v>
-      </c>
+      <c r="Z650" t="inlineStr"/>
+      <c r="AA650" t="inlineStr"/>
     </row>
     <row r="651">
       <c r="A651" t="n">
@@ -52495,8 +52527,12 @@
       <c r="Y652" t="n">
         <v>0</v>
       </c>
-      <c r="Z652" t="inlineStr"/>
-      <c r="AA652" t="inlineStr"/>
+      <c r="Z652" t="n">
+        <v>141724.6057999999</v>
+      </c>
+      <c r="AA652" t="n">
+        <v>-0.4496597849686704</v>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="n">
@@ -52574,12 +52610,8 @@
       <c r="Y653" t="n">
         <v>0</v>
       </c>
-      <c r="Z653" t="n">
-        <v>67716.94000000013</v>
-      </c>
-      <c r="AA653" t="n">
-        <v>-1.934039504078325e-13</v>
-      </c>
+      <c r="Z653" t="inlineStr"/>
+      <c r="AA653" t="inlineStr"/>
     </row>
     <row r="654">
       <c r="A654" t="n">
@@ -52815,12 +52847,8 @@
       <c r="Y656" t="n">
         <v>0</v>
       </c>
-      <c r="Z656" t="n">
-        <v>133203.2835</v>
-      </c>
-      <c r="AA656" t="n">
-        <v>1.233239074696891</v>
-      </c>
+      <c r="Z656" t="inlineStr"/>
+      <c r="AA656" t="inlineStr"/>
     </row>
     <row r="657">
       <c r="A657" t="n">
@@ -52898,8 +52926,12 @@
       <c r="Y657" t="n">
         <v>0</v>
       </c>
-      <c r="Z657" t="inlineStr"/>
-      <c r="AA657" t="inlineStr"/>
+      <c r="Z657" t="n">
+        <v>153103.4876</v>
+      </c>
+      <c r="AA657" t="n">
+        <v>-1.525384216086731</v>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="n">
@@ -52977,8 +53009,12 @@
       <c r="Y658" t="n">
         <v>0</v>
       </c>
-      <c r="Z658" t="inlineStr"/>
-      <c r="AA658" t="inlineStr"/>
+      <c r="Z658" t="n">
+        <v>67716.94000000013</v>
+      </c>
+      <c r="AA658" t="n">
+        <v>-1.934039504078325e-13</v>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="n">
@@ -53214,8 +53250,12 @@
       <c r="Y661" t="n">
         <v>0</v>
       </c>
-      <c r="Z661" t="inlineStr"/>
-      <c r="AA661" t="inlineStr"/>
+      <c r="Z661" t="n">
+        <v>148913.4662999999</v>
+      </c>
+      <c r="AA661" t="n">
+        <v>1.70220911732873</v>
+      </c>
     </row>
     <row r="662">
       <c r="A662" t="n">
@@ -53451,12 +53491,8 @@
       <c r="Y664" t="n">
         <v>0</v>
       </c>
-      <c r="Z664" t="n">
-        <v>118986.9012</v>
-      </c>
-      <c r="AA664" t="n">
-        <v>0.3418222971108938</v>
-      </c>
+      <c r="Z664" t="inlineStr"/>
+      <c r="AA664" t="inlineStr"/>
     </row>
     <row r="665">
       <c r="A665" t="n">
@@ -53534,12 +53570,8 @@
       <c r="Y665" t="n">
         <v>0</v>
       </c>
-      <c r="Z665" t="n">
-        <v>140223.8670000001</v>
-      </c>
-      <c r="AA665" t="n">
-        <v>-0.2034505566562305</v>
-      </c>
+      <c r="Z665" t="inlineStr"/>
+      <c r="AA665" t="inlineStr"/>
     </row>
     <row r="666">
       <c r="A666" t="n">
@@ -53618,10 +53650,10 @@
         <v>0</v>
       </c>
       <c r="Z666" t="n">
-        <v>35777.79030000003</v>
+        <v>34053.73060000002</v>
       </c>
       <c r="AA666" t="n">
-        <v>-35.76435460894957</v>
+        <v>-29.22214363071038</v>
       </c>
     </row>
     <row r="667">
@@ -54175,10 +54207,10 @@
         <v>0</v>
       </c>
       <c r="Z673" t="n">
-        <v>122295.6688</v>
+        <v>121151.2846999999</v>
       </c>
       <c r="AA673" t="n">
-        <v>-6.645839731874329</v>
+        <v>-5.647899211839202</v>
       </c>
     </row>
     <row r="674">
@@ -54336,8 +54368,12 @@
       <c r="Y675" t="n">
         <v>0</v>
       </c>
-      <c r="Z675" t="inlineStr"/>
-      <c r="AA675" t="inlineStr"/>
+      <c r="Z675" t="n">
+        <v>79058.57000000011</v>
+      </c>
+      <c r="AA675" t="n">
+        <v>-1.288454959387299e-13</v>
+      </c>
     </row>
     <row r="676">
       <c r="A676" t="n">
@@ -54415,12 +54451,8 @@
       <c r="Y676" t="n">
         <v>0</v>
       </c>
-      <c r="Z676" t="n">
-        <v>82667.25999999983</v>
-      </c>
-      <c r="AA676" t="n">
-        <v>1.936329660763347e-13</v>
-      </c>
+      <c r="Z676" t="inlineStr"/>
+      <c r="AA676" t="inlineStr"/>
     </row>
     <row r="677">
       <c r="A677" t="n">
@@ -54577,12 +54609,8 @@
       <c r="Y678" t="n">
         <v>0</v>
       </c>
-      <c r="Z678" t="n">
-        <v>111290.6824999999</v>
-      </c>
-      <c r="AA678" t="n">
-        <v>-0.6760082465347936</v>
-      </c>
+      <c r="Z678" t="inlineStr"/>
+      <c r="AA678" t="inlineStr"/>
     </row>
     <row r="679">
       <c r="A679" t="n">
@@ -54660,12 +54688,8 @@
       <c r="Y679" t="n">
         <v>0</v>
       </c>
-      <c r="Z679" t="n">
-        <v>67716.94000000013</v>
-      </c>
-      <c r="AA679" t="n">
-        <v>-1.934039504078325e-13</v>
-      </c>
+      <c r="Z679" t="inlineStr"/>
+      <c r="AA679" t="inlineStr"/>
     </row>
     <row r="680">
       <c r="A680" t="n">
@@ -54901,12 +54925,8 @@
       <c r="Y682" t="n">
         <v>0</v>
       </c>
-      <c r="Z682" t="n">
-        <v>138669.7524000001</v>
-      </c>
-      <c r="AA682" t="n">
-        <v>0.04427815001641104</v>
-      </c>
+      <c r="Z682" t="inlineStr"/>
+      <c r="AA682" t="inlineStr"/>
     </row>
     <row r="683">
       <c r="A683" t="n">
@@ -55064,10 +55084,10 @@
         <v>0</v>
       </c>
       <c r="Z684" t="n">
-        <v>42661.29719999997</v>
+        <v>42700.12329999996</v>
       </c>
       <c r="AA684" t="n">
-        <v>0.5930976984484045</v>
+        <v>0.5026273521915778</v>
       </c>
     </row>
     <row r="685">
@@ -55146,8 +55166,12 @@
       <c r="Y685" t="n">
         <v>0</v>
       </c>
-      <c r="Z685" t="inlineStr"/>
-      <c r="AA685" t="inlineStr"/>
+      <c r="Z685" t="n">
+        <v>159561.1741000001</v>
+      </c>
+      <c r="AA685" t="n">
+        <v>1.128295255159675</v>
+      </c>
     </row>
     <row r="686">
       <c r="A686" t="n">
@@ -56410,12 +56434,8 @@
       <c r="Y701" t="n">
         <v>0</v>
       </c>
-      <c r="Z701" t="n">
-        <v>167121.2072</v>
-      </c>
-      <c r="AA701" t="n">
-        <v>0.4248197328077395</v>
-      </c>
+      <c r="Z701" t="inlineStr"/>
+      <c r="AA701" t="inlineStr"/>
     </row>
     <row r="702">
       <c r="A702" t="n">
@@ -57757,8 +57777,12 @@
       <c r="Y718" t="n">
         <v>0</v>
       </c>
-      <c r="Z718" t="inlineStr"/>
-      <c r="AA718" t="inlineStr"/>
+      <c r="Z718" t="n">
+        <v>123131.8102</v>
+      </c>
+      <c r="AA718" t="n">
+        <v>1.29712239610155</v>
+      </c>
     </row>
     <row r="719">
       <c r="A719" t="n">
@@ -58469,10 +58493,10 @@
         <v>0</v>
       </c>
       <c r="Z727" t="n">
-        <v>115029.6475999999</v>
+        <v>115918.7006999999</v>
       </c>
       <c r="AA727" t="n">
-        <v>-2.22946554968429</v>
+        <v>-3.019587271819259</v>
       </c>
     </row>
     <row r="728">
@@ -58788,8 +58812,12 @@
       <c r="Y731" t="n">
         <v>0</v>
       </c>
-      <c r="Z731" t="inlineStr"/>
-      <c r="AA731" t="inlineStr"/>
+      <c r="Z731" t="n">
+        <v>136333.3507000001</v>
+      </c>
+      <c r="AA731" t="n">
+        <v>0.3109342755678796</v>
+      </c>
     </row>
     <row r="732">
       <c r="A732" t="n">
@@ -58867,12 +58895,8 @@
       <c r="Y732" t="n">
         <v>0</v>
       </c>
-      <c r="Z732" t="n">
-        <v>104279.0941</v>
-      </c>
-      <c r="AA732" t="n">
-        <v>1.946056604359011</v>
-      </c>
+      <c r="Z732" t="inlineStr"/>
+      <c r="AA732" t="inlineStr"/>
     </row>
     <row r="733">
       <c r="A733" t="n">
@@ -58950,8 +58974,12 @@
       <c r="Y733" t="n">
         <v>0</v>
       </c>
-      <c r="Z733" t="inlineStr"/>
-      <c r="AA733" t="inlineStr"/>
+      <c r="Z733" t="n">
+        <v>79058.57000000011</v>
+      </c>
+      <c r="AA733" t="n">
+        <v>-1.288454959387299e-13</v>
+      </c>
     </row>
     <row r="734">
       <c r="A734" t="n">
@@ -59108,12 +59136,8 @@
       <c r="Y735" t="n">
         <v>0</v>
       </c>
-      <c r="Z735" t="n">
-        <v>117246.1045000001</v>
-      </c>
-      <c r="AA735" t="n">
-        <v>2.421001246222942</v>
-      </c>
+      <c r="Z735" t="inlineStr"/>
+      <c r="AA735" t="inlineStr"/>
     </row>
     <row r="736">
       <c r="A736" t="n">
@@ -59349,8 +59373,12 @@
       <c r="Y738" t="n">
         <v>0</v>
       </c>
-      <c r="Z738" t="inlineStr"/>
-      <c r="AA738" t="inlineStr"/>
+      <c r="Z738" t="n">
+        <v>188360.3567000001</v>
+      </c>
+      <c r="AA738" t="n">
+        <v>29.47802579730562</v>
+      </c>
     </row>
     <row r="739">
       <c r="A739" t="n">
@@ -59429,10 +59457,10 @@
         <v>0</v>
       </c>
       <c r="Z739" t="n">
-        <v>59198.27330000002</v>
+        <v>58723.43259999999</v>
       </c>
       <c r="AA739" t="n">
-        <v>-2.468654928124487</v>
+        <v>-1.646734201018872</v>
       </c>
     </row>
     <row r="740">
@@ -59511,8 +59539,12 @@
       <c r="Y740" t="n">
         <v>0</v>
       </c>
-      <c r="Z740" t="inlineStr"/>
-      <c r="AA740" t="inlineStr"/>
+      <c r="Z740" t="n">
+        <v>79241.88339999995</v>
+      </c>
+      <c r="AA740" t="n">
+        <v>-5.855855644044173</v>
+      </c>
     </row>
     <row r="741">
       <c r="A741" t="n">
@@ -60064,12 +60096,8 @@
       <c r="Y747" t="n">
         <v>0</v>
       </c>
-      <c r="Z747" t="n">
-        <v>194305.6829</v>
-      </c>
-      <c r="AA747" t="n">
-        <v>0.004192753547173072</v>
-      </c>
+      <c r="Z747" t="inlineStr"/>
+      <c r="AA747" t="inlineStr"/>
     </row>
     <row r="748">
       <c r="A748" t="n">
@@ -60464,10 +60492,10 @@
         <v>0</v>
       </c>
       <c r="Z752" t="n">
-        <v>98048.95200000012</v>
+        <v>94236.39569999998</v>
       </c>
       <c r="AA752" t="n">
-        <v>-3.135198384068357</v>
+        <v>0.8751326019369179</v>
       </c>
     </row>
     <row r="753">
@@ -60625,8 +60653,12 @@
       <c r="Y754" t="n">
         <v>0</v>
       </c>
-      <c r="Z754" t="inlineStr"/>
-      <c r="AA754" t="inlineStr"/>
+      <c r="Z754" t="n">
+        <v>67716.94000000013</v>
+      </c>
+      <c r="AA754" t="n">
+        <v>-1.934039504078325e-13</v>
+      </c>
     </row>
     <row r="755">
       <c r="A755" t="n">
@@ -61099,12 +61131,8 @@
       <c r="Y760" t="n">
         <v>0</v>
       </c>
-      <c r="Z760" t="n">
-        <v>62577.71999999998</v>
-      </c>
-      <c r="AA760" t="n">
-        <v>3.488122105207776e-14</v>
-      </c>
+      <c r="Z760" t="inlineStr"/>
+      <c r="AA760" t="inlineStr"/>
     </row>
     <row r="761">
       <c r="A761" t="n">
@@ -61656,12 +61684,8 @@
       <c r="Y767" t="n">
         <v>0</v>
       </c>
-      <c r="Z767" t="n">
-        <v>62577.71999999998</v>
-      </c>
-      <c r="AA767" t="n">
-        <v>3.488122105207776e-14</v>
-      </c>
+      <c r="Z767" t="inlineStr"/>
+      <c r="AA767" t="inlineStr"/>
     </row>
     <row r="768">
       <c r="A768" t="n">
@@ -61739,8 +61763,12 @@
       <c r="Y768" t="n">
         <v>0</v>
       </c>
-      <c r="Z768" t="inlineStr"/>
-      <c r="AA768" t="inlineStr"/>
+      <c r="Z768" t="n">
+        <v>158729.7015</v>
+      </c>
+      <c r="AA768" t="n">
+        <v>1.702147285424706</v>
+      </c>
     </row>
     <row r="769">
       <c r="A769" t="n">
@@ -61818,8 +61846,12 @@
       <c r="Y769" t="n">
         <v>0</v>
       </c>
-      <c r="Z769" t="inlineStr"/>
-      <c r="AA769" t="inlineStr"/>
+      <c r="Z769" t="n">
+        <v>67716.94000000013</v>
+      </c>
+      <c r="AA769" t="n">
+        <v>-1.934039504078325e-13</v>
+      </c>
     </row>
     <row r="770">
       <c r="A770" t="n">
@@ -61976,8 +62008,12 @@
       <c r="Y771" t="n">
         <v>0</v>
       </c>
-      <c r="Z771" t="inlineStr"/>
-      <c r="AA771" t="inlineStr"/>
+      <c r="Z771" t="n">
+        <v>223812.4665</v>
+      </c>
+      <c r="AA771" t="n">
+        <v>16.69303835279078</v>
+      </c>
     </row>
     <row r="772">
       <c r="A772" t="n">
@@ -62055,12 +62091,8 @@
       <c r="Y772" t="n">
         <v>0</v>
       </c>
-      <c r="Z772" t="n">
-        <v>126676.7426000001</v>
-      </c>
-      <c r="AA772" t="n">
-        <v>0.07766298140325641</v>
-      </c>
+      <c r="Z772" t="inlineStr"/>
+      <c r="AA772" t="inlineStr"/>
     </row>
     <row r="773">
       <c r="A773" t="n">
@@ -62612,8 +62644,12 @@
       <c r="Y779" t="n">
         <v>0</v>
       </c>
-      <c r="Z779" t="inlineStr"/>
-      <c r="AA779" t="inlineStr"/>
+      <c r="Z779" t="n">
+        <v>155276.6152999999</v>
+      </c>
+      <c r="AA779" t="n">
+        <v>-0.2561826639283021</v>
+      </c>
     </row>
     <row r="780">
       <c r="A780" t="n">
@@ -62691,8 +62727,12 @@
       <c r="Y780" t="n">
         <v>0</v>
       </c>
-      <c r="Z780" t="inlineStr"/>
-      <c r="AA780" t="inlineStr"/>
+      <c r="Z780" t="n">
+        <v>73595.33679999998</v>
+      </c>
+      <c r="AA780" t="n">
+        <v>-2.012966447805391</v>
+      </c>
     </row>
     <row r="781">
       <c r="A781" t="n">
@@ -63007,12 +63047,8 @@
       <c r="Y784" t="n">
         <v>0</v>
       </c>
-      <c r="Z784" t="n">
-        <v>129339.6368000002</v>
-      </c>
-      <c r="AA784" t="n">
-        <v>-3.932588108709386</v>
-      </c>
+      <c r="Z784" t="inlineStr"/>
+      <c r="AA784" t="inlineStr"/>
     </row>
     <row r="785">
       <c r="A785" t="n">
@@ -63090,12 +63126,8 @@
       <c r="Y785" t="n">
         <v>0</v>
       </c>
-      <c r="Z785" t="n">
-        <v>140590.3394</v>
-      </c>
-      <c r="AA785" t="n">
-        <v>-0.7431062724345474</v>
-      </c>
+      <c r="Z785" t="inlineStr"/>
+      <c r="AA785" t="inlineStr"/>
     </row>
     <row r="786">
       <c r="A786" t="n">
@@ -63173,8 +63205,12 @@
       <c r="Y786" t="n">
         <v>0</v>
       </c>
-      <c r="Z786" t="inlineStr"/>
-      <c r="AA786" t="inlineStr"/>
+      <c r="Z786" t="n">
+        <v>124928.0832999999</v>
+      </c>
+      <c r="AA786" t="n">
+        <v>2.537501715352313</v>
+      </c>
     </row>
     <row r="787">
       <c r="A787" t="n">
@@ -63489,8 +63525,12 @@
       <c r="Y790" t="n">
         <v>0</v>
       </c>
-      <c r="Z790" t="inlineStr"/>
-      <c r="AA790" t="inlineStr"/>
+      <c r="Z790" t="n">
+        <v>137706.6256000001</v>
+      </c>
+      <c r="AA790" t="n">
+        <v>0.1714144703742301</v>
+      </c>
     </row>
     <row r="791">
       <c r="A791" t="n">
@@ -63568,12 +63608,8 @@
       <c r="Y791" t="n">
         <v>0</v>
       </c>
-      <c r="Z791" t="n">
-        <v>163256.7873000001</v>
-      </c>
-      <c r="AA791" t="n">
-        <v>5.321374436395602</v>
-      </c>
+      <c r="Z791" t="inlineStr"/>
+      <c r="AA791" t="inlineStr"/>
     </row>
     <row r="792">
       <c r="A792" t="n">
@@ -63730,12 +63766,8 @@
       <c r="Y793" t="n">
         <v>0</v>
       </c>
-      <c r="Z793" t="n">
-        <v>79058.57000000011</v>
-      </c>
-      <c r="AA793" t="n">
-        <v>-1.288454959387299e-13</v>
-      </c>
+      <c r="Z793" t="inlineStr"/>
+      <c r="AA793" t="inlineStr"/>
     </row>
     <row r="794">
       <c r="A794" t="n">
@@ -63892,12 +63924,8 @@
       <c r="Y795" t="n">
         <v>0</v>
       </c>
-      <c r="Z795" t="n">
-        <v>82291.50199999983</v>
-      </c>
-      <c r="AA795" t="n">
-        <v>0.4545427052985205</v>
-      </c>
+      <c r="Z795" t="inlineStr"/>
+      <c r="AA795" t="inlineStr"/>
     </row>
     <row r="796">
       <c r="A796" t="n">
@@ -63975,12 +64003,8 @@
       <c r="Y796" t="n">
         <v>0</v>
       </c>
-      <c r="Z796" t="n">
-        <v>142613.1481999999</v>
-      </c>
-      <c r="AA796" t="n">
-        <v>4.88233562368362</v>
-      </c>
+      <c r="Z796" t="inlineStr"/>
+      <c r="AA796" t="inlineStr"/>
     </row>
     <row r="797">
       <c r="A797" t="n">
@@ -64295,12 +64319,8 @@
       <c r="Y800" t="n">
         <v>0</v>
       </c>
-      <c r="Z800" t="n">
-        <v>82216.35039999984</v>
-      </c>
-      <c r="AA800" t="n">
-        <v>0.5454512463581824</v>
-      </c>
+      <c r="Z800" t="inlineStr"/>
+      <c r="AA800" t="inlineStr"/>
     </row>
     <row r="801">
       <c r="A801" t="n">
@@ -64379,10 +64399,10 @@
         <v>0</v>
       </c>
       <c r="Z801" t="n">
-        <v>111252.4546</v>
+        <v>111108.3424</v>
       </c>
       <c r="AA801" t="n">
-        <v>-2.464041993396899</v>
+        <v>-2.331313968962351</v>
       </c>
     </row>
     <row r="802">
@@ -64619,12 +64639,8 @@
       <c r="Y804" t="n">
         <v>0</v>
       </c>
-      <c r="Z804" t="n">
-        <v>141031.5430000001</v>
-      </c>
-      <c r="AA804" t="n">
-        <v>-0.6694254389134077</v>
-      </c>
+      <c r="Z804" t="inlineStr"/>
+      <c r="AA804" t="inlineStr"/>
     </row>
     <row r="805">
       <c r="A805" t="n">
@@ -64703,10 +64719,10 @@
         <v>0</v>
       </c>
       <c r="Z805" t="n">
-        <v>130306.8096</v>
+        <v>132963.053</v>
       </c>
       <c r="AA805" t="n">
-        <v>3.340756395087903</v>
+        <v>1.370402898883978</v>
       </c>
     </row>
     <row r="806">
@@ -64864,12 +64880,8 @@
       <c r="Y807" t="n">
         <v>0</v>
       </c>
-      <c r="Z807" t="n">
-        <v>82667.25999999983</v>
-      </c>
-      <c r="AA807" t="n">
-        <v>1.936329660763347e-13</v>
-      </c>
+      <c r="Z807" t="inlineStr"/>
+      <c r="AA807" t="inlineStr"/>
     </row>
     <row r="808">
       <c r="A808" t="n">
@@ -65026,8 +65038,12 @@
       <c r="Y809" t="n">
         <v>0</v>
       </c>
-      <c r="Z809" t="inlineStr"/>
-      <c r="AA809" t="inlineStr"/>
+      <c r="Z809" t="n">
+        <v>138708.6679</v>
+      </c>
+      <c r="AA809" t="n">
+        <v>-0.8433289945058051</v>
+      </c>
     </row>
     <row r="810">
       <c r="A810" t="n">
@@ -65184,12 +65200,8 @@
       <c r="Y811" t="n">
         <v>0</v>
       </c>
-      <c r="Z811" t="n">
-        <v>129524.4484</v>
-      </c>
-      <c r="AA811" t="n">
-        <v>-0.158025253462163</v>
-      </c>
+      <c r="Z811" t="inlineStr"/>
+      <c r="AA811" t="inlineStr"/>
     </row>
     <row r="812">
       <c r="A812" t="n">
@@ -65346,8 +65358,12 @@
       <c r="Y813" t="n">
         <v>0</v>
       </c>
-      <c r="Z813" t="inlineStr"/>
-      <c r="AA813" t="inlineStr"/>
+      <c r="Z813" t="n">
+        <v>96204.72469999995</v>
+      </c>
+      <c r="AA813" t="n">
+        <v>2.123435921315636</v>
+      </c>
     </row>
     <row r="814">
       <c r="A814" t="n">
@@ -65583,8 +65599,12 @@
       <c r="Y816" t="n">
         <v>0</v>
       </c>
-      <c r="Z816" t="inlineStr"/>
-      <c r="AA816" t="inlineStr"/>
+      <c r="Z816" t="n">
+        <v>102241.5314</v>
+      </c>
+      <c r="AA816" t="n">
+        <v>-0.1119696049572838</v>
+      </c>
     </row>
     <row r="817">
       <c r="A817" t="n">
@@ -65662,12 +65682,8 @@
       <c r="Y817" t="n">
         <v>0</v>
       </c>
-      <c r="Z817" t="n">
-        <v>62577.71999999998</v>
-      </c>
-      <c r="AA817" t="n">
-        <v>3.488122105207776e-14</v>
-      </c>
+      <c r="Z817" t="inlineStr"/>
+      <c r="AA817" t="inlineStr"/>
     </row>
     <row r="818">
       <c r="A818" t="n">
@@ -65745,8 +65761,12 @@
       <c r="Y818" t="n">
         <v>0</v>
       </c>
-      <c r="Z818" t="inlineStr"/>
-      <c r="AA818" t="inlineStr"/>
+      <c r="Z818" t="n">
+        <v>157791.1107</v>
+      </c>
+      <c r="AA818" t="n">
+        <v>-1.033222593914774</v>
+      </c>
     </row>
     <row r="819">
       <c r="A819" t="n">
@@ -65903,12 +65923,8 @@
       <c r="Y820" t="n">
         <v>0</v>
       </c>
-      <c r="Z820" t="n">
-        <v>95095.37449999996</v>
-      </c>
-      <c r="AA820" t="n">
-        <v>0.2182666324881389</v>
-      </c>
+      <c r="Z820" t="inlineStr"/>
+      <c r="AA820" t="inlineStr"/>
     </row>
     <row r="821">
       <c r="A821" t="n">
@@ -65986,12 +66002,8 @@
       <c r="Y821" t="n">
         <v>0</v>
       </c>
-      <c r="Z821" t="n">
-        <v>150299.8742</v>
-      </c>
-      <c r="AA821" t="n">
-        <v>-0.364594359758836</v>
-      </c>
+      <c r="Z821" t="inlineStr"/>
+      <c r="AA821" t="inlineStr"/>
     </row>
     <row r="822">
       <c r="A822" t="n">
@@ -66069,8 +66081,12 @@
       <c r="Y822" t="n">
         <v>0</v>
       </c>
-      <c r="Z822" t="inlineStr"/>
-      <c r="AA822" t="inlineStr"/>
+      <c r="Z822" t="n">
+        <v>22572.31000000004</v>
+      </c>
+      <c r="AA822" t="n">
+        <v>-1.772869807211085e-13</v>
+      </c>
     </row>
     <row r="823">
       <c r="A823" t="n">
@@ -66148,8 +66164,12 @@
       <c r="Y823" t="n">
         <v>0</v>
       </c>
-      <c r="Z823" t="inlineStr"/>
-      <c r="AA823" t="inlineStr"/>
+      <c r="Z823" t="n">
+        <v>93617.20149999992</v>
+      </c>
+      <c r="AA823" t="n">
+        <v>-1.183337323360158</v>
+      </c>
     </row>
     <row r="824">
       <c r="A824" t="n">
@@ -66227,8 +66247,12 @@
       <c r="Y824" t="n">
         <v>0</v>
       </c>
-      <c r="Z824" t="inlineStr"/>
-      <c r="AA824" t="inlineStr"/>
+      <c r="Z824" t="n">
+        <v>79058.57000000011</v>
+      </c>
+      <c r="AA824" t="n">
+        <v>-1.288454959387299e-13</v>
+      </c>
     </row>
     <row r="825">
       <c r="A825" t="n">
@@ -66385,8 +66409,12 @@
       <c r="Y826" t="n">
         <v>0</v>
       </c>
-      <c r="Z826" t="inlineStr"/>
-      <c r="AA826" t="inlineStr"/>
+      <c r="Z826" t="n">
+        <v>155587.8343000001</v>
+      </c>
+      <c r="AA826" t="n">
+        <v>-1.591927837973093</v>
+      </c>
     </row>
     <row r="827">
       <c r="A827" t="n">
@@ -66543,12 +66571,8 @@
       <c r="Y828" t="n">
         <v>0</v>
       </c>
-      <c r="Z828" t="n">
-        <v>184616.0222</v>
-      </c>
-      <c r="AA828" t="n">
-        <v>11.51910609270841</v>
-      </c>
+      <c r="Z828" t="inlineStr"/>
+      <c r="AA828" t="inlineStr"/>
     </row>
     <row r="829">
       <c r="A829" t="n">
@@ -66626,12 +66650,8 @@
       <c r="Y829" t="n">
         <v>0</v>
       </c>
-      <c r="Z829" t="n">
-        <v>150215.047</v>
-      </c>
-      <c r="AA829" t="n">
-        <v>1.198186122524484</v>
-      </c>
+      <c r="Z829" t="inlineStr"/>
+      <c r="AA829" t="inlineStr"/>
     </row>
     <row r="830">
       <c r="A830" t="n">
@@ -67104,8 +67124,12 @@
       <c r="Y835" t="n">
         <v>0</v>
       </c>
-      <c r="Z835" t="inlineStr"/>
-      <c r="AA835" t="inlineStr"/>
+      <c r="Z835" t="n">
+        <v>79058.57000000011</v>
+      </c>
+      <c r="AA835" t="n">
+        <v>-1.288454959387299e-13</v>
+      </c>
     </row>
     <row r="836">
       <c r="A836" t="n">
@@ -67341,8 +67365,12 @@
       <c r="Y838" t="n">
         <v>0</v>
       </c>
-      <c r="Z838" t="inlineStr"/>
-      <c r="AA838" t="inlineStr"/>
+      <c r="Z838" t="n">
+        <v>110606.5353000001</v>
+      </c>
+      <c r="AA838" t="n">
+        <v>-7.187708311993211</v>
+      </c>
     </row>
     <row r="839">
       <c r="A839" t="n">
@@ -67499,8 +67527,12 @@
       <c r="Y840" t="n">
         <v>0</v>
       </c>
-      <c r="Z840" t="inlineStr"/>
-      <c r="AA840" t="inlineStr"/>
+      <c r="Z840" t="n">
+        <v>104017.4683999999</v>
+      </c>
+      <c r="AA840" t="n">
+        <v>0.1565087215921598</v>
+      </c>
     </row>
     <row r="841">
       <c r="A841" t="n">
@@ -67578,8 +67610,12 @@
       <c r="Y841" t="n">
         <v>0</v>
       </c>
-      <c r="Z841" t="inlineStr"/>
-      <c r="AA841" t="inlineStr"/>
+      <c r="Z841" t="n">
+        <v>73058.59999999987</v>
+      </c>
+      <c r="AA841" t="n">
+        <v>1.792632722982669e-13</v>
+      </c>
     </row>
     <row r="842">
       <c r="A842" t="n">
@@ -67657,12 +67693,8 @@
       <c r="Y842" t="n">
         <v>0</v>
       </c>
-      <c r="Z842" t="n">
-        <v>196191.317</v>
-      </c>
-      <c r="AA842" t="n">
-        <v>2.660643961579533</v>
-      </c>
+      <c r="Z842" t="inlineStr"/>
+      <c r="AA842" t="inlineStr"/>
     </row>
     <row r="843">
       <c r="A843" t="n">
@@ -67819,8 +67851,12 @@
       <c r="Y844" t="n">
         <v>0</v>
       </c>
-      <c r="Z844" t="inlineStr"/>
-      <c r="AA844" t="inlineStr"/>
+      <c r="Z844" t="n">
+        <v>130854.351</v>
+      </c>
+      <c r="AA844" t="n">
+        <v>0.8868675413883168</v>
+      </c>
     </row>
     <row r="845">
       <c r="A845" t="n">
@@ -67977,12 +68013,8 @@
       <c r="Y846" t="n">
         <v>0</v>
       </c>
-      <c r="Z846" t="n">
-        <v>146301.0571999999</v>
-      </c>
-      <c r="AA846" t="n">
-        <v>-0.1023028563365906</v>
-      </c>
+      <c r="Z846" t="inlineStr"/>
+      <c r="AA846" t="inlineStr"/>
     </row>
     <row r="847">
       <c r="A847" t="n">
@@ -68218,8 +68250,12 @@
       <c r="Y849" t="n">
         <v>0</v>
       </c>
-      <c r="Z849" t="inlineStr"/>
-      <c r="AA849" t="inlineStr"/>
+      <c r="Z849" t="n">
+        <v>133242.1384000001</v>
+      </c>
+      <c r="AA849" t="n">
+        <v>-0.1743989952047274</v>
+      </c>
     </row>
     <row r="850">
       <c r="A850" t="n">
@@ -68376,8 +68412,12 @@
       <c r="Y851" t="n">
         <v>0</v>
       </c>
-      <c r="Z851" t="inlineStr"/>
-      <c r="AA851" t="inlineStr"/>
+      <c r="Z851" t="n">
+        <v>264544.8683999999</v>
+      </c>
+      <c r="AA851" t="n">
+        <v>47.06598111830633</v>
+      </c>
     </row>
     <row r="852">
       <c r="A852" t="n">
@@ -68534,8 +68574,12 @@
       <c r="Y853" t="n">
         <v>0</v>
       </c>
-      <c r="Z853" t="inlineStr"/>
-      <c r="AA853" t="inlineStr"/>
+      <c r="Z853" t="n">
+        <v>79058.57000000011</v>
+      </c>
+      <c r="AA853" t="n">
+        <v>-1.288454959387299e-13</v>
+      </c>
     </row>
     <row r="854">
       <c r="A854" t="n">
@@ -68613,8 +68657,12 @@
       <c r="Y854" t="n">
         <v>0</v>
       </c>
-      <c r="Z854" t="inlineStr"/>
-      <c r="AA854" t="inlineStr"/>
+      <c r="Z854" t="n">
+        <v>67716.94000000013</v>
+      </c>
+      <c r="AA854" t="n">
+        <v>-1.934039504078325e-13</v>
+      </c>
     </row>
     <row r="855">
       <c r="A855" t="n">
@@ -68692,12 +68740,8 @@
       <c r="Y855" t="n">
         <v>0</v>
       </c>
-      <c r="Z855" t="n">
-        <v>67716.94000000013</v>
-      </c>
-      <c r="AA855" t="n">
-        <v>-1.934039504078325e-13</v>
-      </c>
+      <c r="Z855" t="inlineStr"/>
+      <c r="AA855" t="inlineStr"/>
     </row>
     <row r="856">
       <c r="A856" t="n">
@@ -68934,10 +68978,10 @@
         <v>0</v>
       </c>
       <c r="Z858" t="n">
-        <v>129260.1031999999</v>
+        <v>130062.1774999999</v>
       </c>
       <c r="AA858" t="n">
-        <v>-1.71222246930254</v>
+        <v>-2.343358895925131</v>
       </c>
     </row>
     <row r="859">
@@ -69016,8 +69060,12 @@
       <c r="Y859" t="n">
         <v>0</v>
       </c>
-      <c r="Z859" t="inlineStr"/>
-      <c r="AA859" t="inlineStr"/>
+      <c r="Z859" t="n">
+        <v>121251.2782</v>
+      </c>
+      <c r="AA859" t="n">
+        <v>-0.4308568380475365</v>
+      </c>
     </row>
     <row r="860">
       <c r="A860" t="n">
@@ -69095,8 +69143,12 @@
       <c r="Y860" t="n">
         <v>0</v>
       </c>
-      <c r="Z860" t="inlineStr"/>
-      <c r="AA860" t="inlineStr"/>
+      <c r="Z860" t="n">
+        <v>144850.7826999999</v>
+      </c>
+      <c r="AA860" t="n">
+        <v>6.048557488307929</v>
+      </c>
     </row>
     <row r="861">
       <c r="A861" t="n">
@@ -69253,12 +69305,8 @@
       <c r="Y862" t="n">
         <v>0</v>
       </c>
-      <c r="Z862" t="n">
-        <v>82216.35039999984</v>
-      </c>
-      <c r="AA862" t="n">
-        <v>0.5454512463581824</v>
-      </c>
+      <c r="Z862" t="inlineStr"/>
+      <c r="AA862" t="inlineStr"/>
     </row>
     <row r="863">
       <c r="A863" t="n">
@@ -69652,8 +69700,12 @@
       <c r="Y867" t="n">
         <v>0</v>
       </c>
-      <c r="Z867" t="inlineStr"/>
-      <c r="AA867" t="inlineStr"/>
+      <c r="Z867" t="n">
+        <v>164570.0730000004</v>
+      </c>
+      <c r="AA867" t="n">
+        <v>0.2183088074929981</v>
+      </c>
     </row>
     <row r="868">
       <c r="A868" t="n">
@@ -70205,8 +70257,12 @@
       <c r="Y874" t="n">
         <v>0</v>
       </c>
-      <c r="Z874" t="inlineStr"/>
-      <c r="AA874" t="inlineStr"/>
+      <c r="Z874" t="n">
+        <v>79058.57000000011</v>
+      </c>
+      <c r="AA874" t="n">
+        <v>-1.288454959387299e-13</v>
+      </c>
     </row>
     <row r="875">
       <c r="A875" t="n">
@@ -70363,8 +70419,12 @@
       <c r="Y876" t="n">
         <v>0</v>
       </c>
-      <c r="Z876" t="inlineStr"/>
-      <c r="AA876" t="inlineStr"/>
+      <c r="Z876" t="n">
+        <v>79058.57000000011</v>
+      </c>
+      <c r="AA876" t="n">
+        <v>-1.288454959387299e-13</v>
+      </c>
     </row>
     <row r="877">
       <c r="A877" t="n">
@@ -70916,12 +70976,8 @@
       <c r="Y883" t="n">
         <v>0</v>
       </c>
-      <c r="Z883" t="n">
-        <v>155706.3913999999</v>
-      </c>
-      <c r="AA883" t="n">
-        <v>1.886164897697119</v>
-      </c>
+      <c r="Z883" t="inlineStr"/>
+      <c r="AA883" t="inlineStr"/>
     </row>
     <row r="884">
       <c r="A884" t="n">
@@ -70999,8 +71055,12 @@
       <c r="Y884" t="n">
         <v>0</v>
       </c>
-      <c r="Z884" t="inlineStr"/>
-      <c r="AA884" t="inlineStr"/>
+      <c r="Z884" t="n">
+        <v>309596.6792999999</v>
+      </c>
+      <c r="AA884" t="n">
+        <v>25.09710582128749</v>
+      </c>
     </row>
     <row r="885">
       <c r="A885" t="n">
@@ -71236,8 +71296,12 @@
       <c r="Y887" t="n">
         <v>0</v>
       </c>
-      <c r="Z887" t="inlineStr"/>
-      <c r="AA887" t="inlineStr"/>
+      <c r="Z887" t="n">
+        <v>124540.1497999999</v>
+      </c>
+      <c r="AA887" t="n">
+        <v>0.006648176938191274</v>
+      </c>
     </row>
     <row r="888">
       <c r="A888" t="n">
@@ -71315,12 +71379,8 @@
       <c r="Y888" t="n">
         <v>0</v>
       </c>
-      <c r="Z888" t="n">
-        <v>79058.57000000011</v>
-      </c>
-      <c r="AA888" t="n">
-        <v>-1.288454959387299e-13</v>
-      </c>
+      <c r="Z888" t="inlineStr"/>
+      <c r="AA888" t="inlineStr"/>
     </row>
     <row r="889">
       <c r="A889" t="n">
@@ -71398,8 +71458,12 @@
       <c r="Y889" t="n">
         <v>0</v>
       </c>
-      <c r="Z889" t="inlineStr"/>
-      <c r="AA889" t="inlineStr"/>
+      <c r="Z889" t="n">
+        <v>82667.25999999983</v>
+      </c>
+      <c r="AA889" t="n">
+        <v>1.936329660763347e-13</v>
+      </c>
     </row>
     <row r="890">
       <c r="A890" t="n">
@@ -71635,8 +71699,12 @@
       <c r="Y892" t="n">
         <v>0</v>
       </c>
-      <c r="Z892" t="inlineStr"/>
-      <c r="AA892" t="inlineStr"/>
+      <c r="Z892" t="n">
+        <v>79058.57000000011</v>
+      </c>
+      <c r="AA892" t="n">
+        <v>-1.288454959387299e-13</v>
+      </c>
     </row>
     <row r="893">
       <c r="A893" t="n">
@@ -71794,10 +71862,10 @@
         <v>0</v>
       </c>
       <c r="Z894" t="n">
-        <v>160786.1254</v>
+        <v>160831.8203000002</v>
       </c>
       <c r="AA894" t="n">
-        <v>0.6150435943866349</v>
+        <v>0.5867987092438318</v>
       </c>
     </row>
     <row r="895">
@@ -71955,12 +72023,8 @@
       <c r="Y896" t="n">
         <v>0</v>
       </c>
-      <c r="Z896" t="n">
-        <v>153214.5677999999</v>
-      </c>
-      <c r="AA896" t="n">
-        <v>-0.2026083293542393</v>
-      </c>
+      <c r="Z896" t="inlineStr"/>
+      <c r="AA896" t="inlineStr"/>
     </row>
     <row r="897">
       <c r="A897" t="n">
@@ -72118,10 +72182,10 @@
         <v>0</v>
       </c>
       <c r="Z898" t="n">
-        <v>122661.2416</v>
+        <v>124086.5145</v>
       </c>
       <c r="AA898" t="n">
-        <v>-0.7402200805765985</v>
+        <v>-1.910779776108689</v>
       </c>
     </row>
     <row r="899">
@@ -72437,8 +72501,12 @@
       <c r="Y902" t="n">
         <v>0</v>
       </c>
-      <c r="Z902" t="inlineStr"/>
-      <c r="AA902" t="inlineStr"/>
+      <c r="Z902" t="n">
+        <v>103046.3488999999</v>
+      </c>
+      <c r="AA902" t="n">
+        <v>-1.294361621396235</v>
+      </c>
     </row>
     <row r="903">
       <c r="A903" t="n">
@@ -72516,12 +72584,8 @@
       <c r="Y903" t="n">
         <v>0</v>
       </c>
-      <c r="Z903" t="n">
-        <v>76393.42999999989</v>
-      </c>
-      <c r="AA903" t="n">
-        <v>1.333405328161963e-13</v>
-      </c>
+      <c r="Z903" t="inlineStr"/>
+      <c r="AA903" t="inlineStr"/>
     </row>
     <row r="904">
       <c r="A904" t="n">
@@ -72994,12 +73058,8 @@
       <c r="Y909" t="n">
         <v>0</v>
       </c>
-      <c r="Z909" t="n">
-        <v>183238.6054000001</v>
-      </c>
-      <c r="AA909" t="n">
-        <v>-14.5969619066018</v>
-      </c>
+      <c r="Z909" t="inlineStr"/>
+      <c r="AA909" t="inlineStr"/>
     </row>
     <row r="910">
       <c r="A910" t="n">
@@ -73235,8 +73295,12 @@
       <c r="Y912" t="n">
         <v>0</v>
       </c>
-      <c r="Z912" t="inlineStr"/>
-      <c r="AA912" t="inlineStr"/>
+      <c r="Z912" t="n">
+        <v>67716.94000000013</v>
+      </c>
+      <c r="AA912" t="n">
+        <v>-1.934039504078325e-13</v>
+      </c>
     </row>
     <row r="913">
       <c r="A913" t="n">
@@ -73393,8 +73457,12 @@
       <c r="Y914" t="n">
         <v>0</v>
       </c>
-      <c r="Z914" t="inlineStr"/>
-      <c r="AA914" t="inlineStr"/>
+      <c r="Z914" t="n">
+        <v>167049.0283</v>
+      </c>
+      <c r="AA914" t="n">
+        <v>1.306770767114054</v>
+      </c>
     </row>
     <row r="915">
       <c r="A915" t="n">
@@ -73710,10 +73778,10 @@
         <v>0</v>
       </c>
       <c r="Z918" t="n">
-        <v>253093.1403000001</v>
+        <v>267128.2488000001</v>
       </c>
       <c r="AA918" t="n">
-        <v>39.24485761354821</v>
+        <v>35.87572238405892</v>
       </c>
     </row>
     <row r="919">
@@ -73871,8 +73939,12 @@
       <c r="Y920" t="n">
         <v>0</v>
       </c>
-      <c r="Z920" t="inlineStr"/>
-      <c r="AA920" t="inlineStr"/>
+      <c r="Z920" t="n">
+        <v>67716.94000000013</v>
+      </c>
+      <c r="AA920" t="n">
+        <v>-1.934039504078325e-13</v>
+      </c>
     </row>
     <row r="921">
       <c r="A921" t="n">
@@ -74266,8 +74338,12 @@
       <c r="Y925" t="n">
         <v>0</v>
       </c>
-      <c r="Z925" t="inlineStr"/>
-      <c r="AA925" t="inlineStr"/>
+      <c r="Z925" t="n">
+        <v>104072.1329</v>
+      </c>
+      <c r="AA925" t="n">
+        <v>1.195294174610221</v>
+      </c>
     </row>
     <row r="926">
       <c r="A926" t="n">
@@ -74345,8 +74421,12 @@
       <c r="Y926" t="n">
         <v>0</v>
       </c>
-      <c r="Z926" t="inlineStr"/>
-      <c r="AA926" t="inlineStr"/>
+      <c r="Z926" t="n">
+        <v>79058.57000000011</v>
+      </c>
+      <c r="AA926" t="n">
+        <v>-1.288454959387299e-13</v>
+      </c>
     </row>
     <row r="927">
       <c r="A927" t="n">
@@ -74424,8 +74504,12 @@
       <c r="Y927" t="n">
         <v>0</v>
       </c>
-      <c r="Z927" t="inlineStr"/>
-      <c r="AA927" t="inlineStr"/>
+      <c r="Z927" t="n">
+        <v>82667.25999999983</v>
+      </c>
+      <c r="AA927" t="n">
+        <v>1.936329660763347e-13</v>
+      </c>
     </row>
     <row r="928">
       <c r="A928" t="n">
@@ -74740,8 +74824,12 @@
       <c r="Y931" t="n">
         <v>0</v>
       </c>
-      <c r="Z931" t="inlineStr"/>
-      <c r="AA931" t="inlineStr"/>
+      <c r="Z931" t="n">
+        <v>145933.1922</v>
+      </c>
+      <c r="AA931" t="n">
+        <v>-1.379948842211131</v>
+      </c>
     </row>
     <row r="932">
       <c r="A932" t="n">
@@ -75372,8 +75460,12 @@
       <c r="Y939" t="n">
         <v>0</v>
       </c>
-      <c r="Z939" t="inlineStr"/>
-      <c r="AA939" t="inlineStr"/>
+      <c r="Z939" t="n">
+        <v>155842.8004000001</v>
+      </c>
+      <c r="AA939" t="n">
+        <v>4.281577851508819</v>
+      </c>
     </row>
     <row r="940">
       <c r="A940" t="n">
@@ -75451,12 +75543,8 @@
       <c r="Y940" t="n">
         <v>0</v>
       </c>
-      <c r="Z940" t="n">
-        <v>145158.277</v>
-      </c>
-      <c r="AA940" t="n">
-        <v>-1.468569464923793</v>
-      </c>
+      <c r="Z940" t="inlineStr"/>
+      <c r="AA940" t="inlineStr"/>
     </row>
     <row r="941">
       <c r="A941" t="n">
@@ -75850,12 +75938,8 @@
       <c r="Y945" t="n">
         <v>0</v>
       </c>
-      <c r="Z945" t="n">
-        <v>34334.71930000004</v>
-      </c>
-      <c r="AA945" t="n">
-        <v>0.5442252321666325</v>
-      </c>
+      <c r="Z945" t="inlineStr"/>
+      <c r="AA945" t="inlineStr"/>
     </row>
     <row r="946">
       <c r="A946" t="n">
@@ -75933,12 +76017,8 @@
       <c r="Y946" t="n">
         <v>0</v>
       </c>
-      <c r="Z946" t="n">
-        <v>123997.795</v>
-      </c>
-      <c r="AA946" t="n">
-        <v>0.1871725034596748</v>
-      </c>
+      <c r="Z946" t="inlineStr"/>
+      <c r="AA946" t="inlineStr"/>
     </row>
     <row r="947">
       <c r="A947" t="n">
@@ -76016,12 +76096,8 @@
       <c r="Y947" t="n">
         <v>0</v>
       </c>
-      <c r="Z947" t="n">
-        <v>147474.2244000002</v>
-      </c>
-      <c r="AA947" t="n">
-        <v>6.501509709787498</v>
-      </c>
+      <c r="Z947" t="inlineStr"/>
+      <c r="AA947" t="inlineStr"/>
     </row>
     <row r="948">
       <c r="A948" t="n">
@@ -76257,12 +76333,8 @@
       <c r="Y950" t="n">
         <v>0</v>
       </c>
-      <c r="Z950" t="n">
-        <v>79058.57000000011</v>
-      </c>
-      <c r="AA950" t="n">
-        <v>-1.288454959387299e-13</v>
-      </c>
+      <c r="Z950" t="inlineStr"/>
+      <c r="AA950" t="inlineStr"/>
     </row>
     <row r="951">
       <c r="A951" t="n">
@@ -76893,12 +76965,8 @@
       <c r="Y958" t="n">
         <v>0</v>
       </c>
-      <c r="Z958" t="n">
-        <v>79058.57000000011</v>
-      </c>
-      <c r="AA958" t="n">
-        <v>-1.288454959387299e-13</v>
-      </c>
+      <c r="Z958" t="inlineStr"/>
+      <c r="AA958" t="inlineStr"/>
     </row>
     <row r="959">
       <c r="A959" t="n">
@@ -77134,12 +77202,8 @@
       <c r="Y961" t="n">
         <v>0</v>
       </c>
-      <c r="Z961" t="n">
-        <v>79058.57000000011</v>
-      </c>
-      <c r="AA961" t="n">
-        <v>-1.288454959387299e-13</v>
-      </c>
+      <c r="Z961" t="inlineStr"/>
+      <c r="AA961" t="inlineStr"/>
     </row>
     <row r="962">
       <c r="A962" t="n">
@@ -77533,12 +77597,8 @@
       <c r="Y966" t="n">
         <v>0</v>
       </c>
-      <c r="Z966" t="n">
-        <v>74192.44219999989</v>
-      </c>
-      <c r="AA966" t="n">
-        <v>-1.551962671061152</v>
-      </c>
+      <c r="Z966" t="inlineStr"/>
+      <c r="AA966" t="inlineStr"/>
     </row>
     <row r="967">
       <c r="A967" t="n">
@@ -77936,8 +77996,12 @@
       <c r="Y971" t="n">
         <v>0</v>
       </c>
-      <c r="Z971" t="inlineStr"/>
-      <c r="AA971" t="inlineStr"/>
+      <c r="Z971" t="n">
+        <v>125576.0531</v>
+      </c>
+      <c r="AA971" t="n">
+        <v>-1.186903031488225</v>
+      </c>
     </row>
     <row r="972">
       <c r="A972" t="n">
@@ -78805,12 +78869,8 @@
       <c r="Y982" t="n">
         <v>0</v>
       </c>
-      <c r="Z982" t="n">
-        <v>76393.42999999989</v>
-      </c>
-      <c r="AA982" t="n">
-        <v>1.333405328161963e-13</v>
-      </c>
+      <c r="Z982" t="inlineStr"/>
+      <c r="AA982" t="inlineStr"/>
     </row>
     <row r="983">
       <c r="A983" t="n">
@@ -78888,8 +78948,12 @@
       <c r="Y983" t="n">
         <v>0</v>
       </c>
-      <c r="Z983" t="inlineStr"/>
-      <c r="AA983" t="inlineStr"/>
+      <c r="Z983" t="n">
+        <v>79058.57000000011</v>
+      </c>
+      <c r="AA983" t="n">
+        <v>-1.288454959387299e-13</v>
+      </c>
     </row>
     <row r="984">
       <c r="A984" t="n">
@@ -79283,12 +79347,8 @@
       <c r="Y988" t="n">
         <v>0</v>
       </c>
-      <c r="Z988" t="n">
-        <v>211090.1181</v>
-      </c>
-      <c r="AA988" t="n">
-        <v>-6.777711630837537</v>
-      </c>
+      <c r="Z988" t="inlineStr"/>
+      <c r="AA988" t="inlineStr"/>
     </row>
     <row r="989">
       <c r="A989" t="n">
@@ -79524,8 +79584,12 @@
       <c r="Y991" t="n">
         <v>0</v>
       </c>
-      <c r="Z991" t="inlineStr"/>
-      <c r="AA991" t="inlineStr"/>
+      <c r="Z991" t="n">
+        <v>22572.31000000004</v>
+      </c>
+      <c r="AA991" t="n">
+        <v>-1.772869807211085e-13</v>
+      </c>
     </row>
     <row r="992">
       <c r="A992" t="n">
@@ -79682,8 +79746,12 @@
       <c r="Y993" t="n">
         <v>0</v>
       </c>
-      <c r="Z993" t="inlineStr"/>
-      <c r="AA993" t="inlineStr"/>
+      <c r="Z993" t="n">
+        <v>129400.4326999999</v>
+      </c>
+      <c r="AA993" t="n">
+        <v>1.29853569163458</v>
+      </c>
     </row>
     <row r="994">
       <c r="A994" t="n">
@@ -79999,10 +80067,10 @@
         <v>0</v>
       </c>
       <c r="Z997" t="n">
-        <v>118483.6652000001</v>
+        <v>118272.9338</v>
       </c>
       <c r="AA997" t="n">
-        <v>0.01742957556308207</v>
+        <v>0.1952554978586257</v>
       </c>
     </row>
     <row r="998">
@@ -80081,8 +80149,12 @@
       <c r="Y998" t="n">
         <v>0</v>
       </c>
-      <c r="Z998" t="inlineStr"/>
-      <c r="AA998" t="inlineStr"/>
+      <c r="Z998" t="n">
+        <v>122342.5163999999</v>
+      </c>
+      <c r="AA998" t="n">
+        <v>-1.48850596214033</v>
+      </c>
     </row>
     <row r="999">
       <c r="A999" t="n">
@@ -80239,8 +80311,12 @@
       <c r="Y1000" t="n">
         <v>0</v>
       </c>
-      <c r="Z1000" t="inlineStr"/>
-      <c r="AA1000" t="inlineStr"/>
+      <c r="Z1000" t="n">
+        <v>137383.2642000001</v>
+      </c>
+      <c r="AA1000" t="n">
+        <v>1.072062875714477</v>
+      </c>
     </row>
     <row r="1001">
       <c r="A1001" t="n">
@@ -81029,8 +81105,12 @@
       <c r="Y1010" t="n">
         <v>0</v>
       </c>
-      <c r="Z1010" t="inlineStr"/>
-      <c r="AA1010" t="inlineStr"/>
+      <c r="Z1010" t="n">
+        <v>250387.8996999998</v>
+      </c>
+      <c r="AA1010" t="n">
+        <v>3.728283286603087</v>
+      </c>
     </row>
     <row r="1011">
       <c r="A1011" t="n">
@@ -81108,12 +81188,8 @@
       <c r="Y1011" t="n">
         <v>0</v>
       </c>
-      <c r="Z1011" t="n">
-        <v>102158.3055</v>
-      </c>
-      <c r="AA1011" t="n">
-        <v>0.6861330324313866</v>
-      </c>
+      <c r="Z1011" t="inlineStr"/>
+      <c r="AA1011" t="inlineStr"/>
     </row>
     <row r="1012">
       <c r="A1012" t="n">
@@ -81586,12 +81662,8 @@
       <c r="Y1017" t="n">
         <v>0</v>
       </c>
-      <c r="Z1017" t="n">
-        <v>82166.79160000003</v>
-      </c>
-      <c r="AA1017" t="n">
-        <v>-0.6914632804322419</v>
-      </c>
+      <c r="Z1017" t="inlineStr"/>
+      <c r="AA1017" t="inlineStr"/>
     </row>
     <row r="1018">
       <c r="A1018" t="n">
@@ -81985,12 +82057,8 @@
       <c r="Y1022" t="n">
         <v>0</v>
       </c>
-      <c r="Z1022" t="n">
-        <v>42673.7368</v>
-      </c>
-      <c r="AA1022" t="n">
-        <v>-1.939370138178222</v>
-      </c>
+      <c r="Z1022" t="inlineStr"/>
+      <c r="AA1022" t="inlineStr"/>
     </row>
     <row r="1023">
       <c r="A1023" t="n">
@@ -82226,12 +82294,8 @@
       <c r="Y1025" t="n">
         <v>0</v>
       </c>
-      <c r="Z1025" t="n">
-        <v>121707.5452</v>
-      </c>
-      <c r="AA1025" t="n">
-        <v>0.5020409714878654</v>
-      </c>
+      <c r="Z1025" t="inlineStr"/>
+      <c r="AA1025" t="inlineStr"/>
     </row>
     <row r="1026">
       <c r="A1026" t="n">
@@ -82388,8 +82452,12 @@
       <c r="Y1027" t="n">
         <v>0</v>
       </c>
-      <c r="Z1027" t="inlineStr"/>
-      <c r="AA1027" t="inlineStr"/>
+      <c r="Z1027" t="n">
+        <v>82667.25999999983</v>
+      </c>
+      <c r="AA1027" t="n">
+        <v>1.936329660763347e-13</v>
+      </c>
     </row>
     <row r="1028">
       <c r="A1028" t="n">
@@ -82625,8 +82693,12 @@
       <c r="Y1030" t="n">
         <v>0</v>
       </c>
-      <c r="Z1030" t="inlineStr"/>
-      <c r="AA1030" t="inlineStr"/>
+      <c r="Z1030" t="n">
+        <v>73058.59999999987</v>
+      </c>
+      <c r="AA1030" t="n">
+        <v>1.792632722982669e-13</v>
+      </c>
     </row>
     <row r="1031">
       <c r="A1031" t="n">
@@ -82941,12 +83013,8 @@
       <c r="Y1034" t="n">
         <v>0</v>
       </c>
-      <c r="Z1034" t="n">
-        <v>128336.4603</v>
-      </c>
-      <c r="AA1034" t="n">
-        <v>-0.8267172715415555</v>
-      </c>
+      <c r="Z1034" t="inlineStr"/>
+      <c r="AA1034" t="inlineStr"/>
     </row>
     <row r="1035">
       <c r="A1035" t="n">
@@ -83024,8 +83092,12 @@
       <c r="Y1035" t="n">
         <v>0</v>
       </c>
-      <c r="Z1035" t="inlineStr"/>
-      <c r="AA1035" t="inlineStr"/>
+      <c r="Z1035" t="n">
+        <v>95095.37449999996</v>
+      </c>
+      <c r="AA1035" t="n">
+        <v>0.2182666324881389</v>
+      </c>
     </row>
     <row r="1036">
       <c r="A1036" t="n">
@@ -83261,12 +83333,8 @@
       <c r="Y1038" t="n">
         <v>0</v>
       </c>
-      <c r="Z1038" t="n">
-        <v>336140.8360999998</v>
-      </c>
-      <c r="AA1038" t="n">
-        <v>9.451723630668187</v>
-      </c>
+      <c r="Z1038" t="inlineStr"/>
+      <c r="AA1038" t="inlineStr"/>
     </row>
     <row r="1039">
       <c r="A1039" t="n">
@@ -83502,8 +83570,12 @@
       <c r="Y1041" t="n">
         <v>0</v>
       </c>
-      <c r="Z1041" t="inlineStr"/>
-      <c r="AA1041" t="inlineStr"/>
+      <c r="Z1041" t="n">
+        <v>157349.3949999999</v>
+      </c>
+      <c r="AA1041" t="n">
+        <v>-2.280400178885708</v>
+      </c>
     </row>
     <row r="1042">
       <c r="A1042" t="n">
@@ -83581,8 +83653,12 @@
       <c r="Y1042" t="n">
         <v>0</v>
       </c>
-      <c r="Z1042" t="inlineStr"/>
-      <c r="AA1042" t="inlineStr"/>
+      <c r="Z1042" t="n">
+        <v>181717.7168</v>
+      </c>
+      <c r="AA1042" t="n">
+        <v>-9.054667909900701</v>
+      </c>
     </row>
     <row r="1043">
       <c r="A1043" t="n">
@@ -83660,8 +83736,12 @@
       <c r="Y1043" t="n">
         <v>0</v>
       </c>
-      <c r="Z1043" t="inlineStr"/>
-      <c r="AA1043" t="inlineStr"/>
+      <c r="Z1043" t="n">
+        <v>79058.57000000011</v>
+      </c>
+      <c r="AA1043" t="n">
+        <v>-1.288454959387299e-13</v>
+      </c>
     </row>
     <row r="1044">
       <c r="A1044" t="n">
@@ -84214,10 +84294,10 @@
         <v>0</v>
       </c>
       <c r="Z1050" t="n">
-        <v>35775.74790000003</v>
+        <v>34049.64580000003</v>
       </c>
       <c r="AA1050" t="n">
-        <v>-35.75660440650476</v>
+        <v>-29.20664322582075</v>
       </c>
     </row>
     <row r="1051">
@@ -84770,8 +84850,12 @@
       <c r="Y1057" t="n">
         <v>0</v>
       </c>
-      <c r="Z1057" t="inlineStr"/>
-      <c r="AA1057" t="inlineStr"/>
+      <c r="Z1057" t="n">
+        <v>62577.71999999998</v>
+      </c>
+      <c r="AA1057" t="n">
+        <v>3.488122105207776e-14</v>
+      </c>
     </row>
     <row r="1058">
       <c r="A1058" t="n">
@@ -84849,12 +84933,8 @@
       <c r="Y1058" t="n">
         <v>0</v>
       </c>
-      <c r="Z1058" t="n">
-        <v>175441.7203</v>
-      </c>
-      <c r="AA1058" t="n">
-        <v>-1.758294808939454</v>
-      </c>
+      <c r="Z1058" t="inlineStr"/>
+      <c r="AA1058" t="inlineStr"/>
     </row>
     <row r="1059">
       <c r="A1059" t="n">
@@ -84932,8 +85012,12 @@
       <c r="Y1059" t="n">
         <v>0</v>
       </c>
-      <c r="Z1059" t="inlineStr"/>
-      <c r="AA1059" t="inlineStr"/>
+      <c r="Z1059" t="n">
+        <v>171169.9862999999</v>
+      </c>
+      <c r="AA1059" t="n">
+        <v>0.2206104001879003</v>
+      </c>
     </row>
     <row r="1060">
       <c r="A1060" t="n">
@@ -85011,8 +85095,12 @@
       <c r="Y1060" t="n">
         <v>0</v>
       </c>
-      <c r="Z1060" t="inlineStr"/>
-      <c r="AA1060" t="inlineStr"/>
+      <c r="Z1060" t="n">
+        <v>100597.135</v>
+      </c>
+      <c r="AA1060" t="n">
+        <v>0.224862470536525</v>
+      </c>
     </row>
     <row r="1061">
       <c r="A1061" t="n">
@@ -85406,12 +85494,8 @@
       <c r="Y1065" t="n">
         <v>0</v>
       </c>
-      <c r="Z1065" t="n">
-        <v>136609.5336</v>
-      </c>
-      <c r="AA1065" t="n">
-        <v>-1.151269607889932</v>
-      </c>
+      <c r="Z1065" t="inlineStr"/>
+      <c r="AA1065" t="inlineStr"/>
     </row>
     <row r="1066">
       <c r="A1066" t="n">
@@ -85489,12 +85573,8 @@
       <c r="Y1066" t="n">
         <v>0</v>
       </c>
-      <c r="Z1066" t="n">
-        <v>73058.59999999987</v>
-      </c>
-      <c r="AA1066" t="n">
-        <v>1.792632722982669e-13</v>
-      </c>
+      <c r="Z1066" t="inlineStr"/>
+      <c r="AA1066" t="inlineStr"/>
     </row>
     <row r="1067">
       <c r="A1067" t="n">
@@ -85651,12 +85731,8 @@
       <c r="Y1068" t="n">
         <v>0</v>
       </c>
-      <c r="Z1068" t="n">
-        <v>104823.8328</v>
-      </c>
-      <c r="AA1068" t="n">
-        <v>0.7695683264862955</v>
-      </c>
+      <c r="Z1068" t="inlineStr"/>
+      <c r="AA1068" t="inlineStr"/>
     </row>
     <row r="1069">
       <c r="A1069" t="n">
@@ -85735,10 +85811,10 @@
         <v>0</v>
       </c>
       <c r="Z1069" t="n">
-        <v>115627.9993000001</v>
+        <v>113950.5879000001</v>
       </c>
       <c r="AA1069" t="n">
-        <v>-0.1508388849744403</v>
+        <v>1.30204588240228</v>
       </c>
     </row>
     <row r="1070">
@@ -85896,8 +85972,12 @@
       <c r="Y1071" t="n">
         <v>0</v>
       </c>
-      <c r="Z1071" t="inlineStr"/>
-      <c r="AA1071" t="inlineStr"/>
+      <c r="Z1071" t="n">
+        <v>73058.59999999987</v>
+      </c>
+      <c r="AA1071" t="n">
+        <v>1.792632722982669e-13</v>
+      </c>
     </row>
     <row r="1072">
       <c r="A1072" t="n">
@@ -85975,12 +86055,8 @@
       <c r="Y1072" t="n">
         <v>0</v>
       </c>
-      <c r="Z1072" t="n">
-        <v>133056.2078</v>
-      </c>
-      <c r="AA1072" t="n">
-        <v>0.07229471597485003</v>
-      </c>
+      <c r="Z1072" t="inlineStr"/>
+      <c r="AA1072" t="inlineStr"/>
     </row>
     <row r="1073">
       <c r="A1073" t="n">
@@ -86216,12 +86292,8 @@
       <c r="Y1075" t="n">
         <v>0</v>
       </c>
-      <c r="Z1075" t="n">
-        <v>67716.94000000013</v>
-      </c>
-      <c r="AA1075" t="n">
-        <v>-1.934039504078325e-13</v>
-      </c>
+      <c r="Z1075" t="inlineStr"/>
+      <c r="AA1075" t="inlineStr"/>
     </row>
     <row r="1076">
       <c r="A1076" t="n">
@@ -86299,12 +86371,8 @@
       <c r="Y1076" t="n">
         <v>0</v>
       </c>
-      <c r="Z1076" t="n">
-        <v>91143.08000000006</v>
-      </c>
-      <c r="AA1076" t="n">
-        <v>-6.386404860738457e-14</v>
-      </c>
+      <c r="Z1076" t="inlineStr"/>
+      <c r="AA1076" t="inlineStr"/>
     </row>
     <row r="1077">
       <c r="A1077" t="n">
@@ -86461,8 +86529,12 @@
       <c r="Y1078" t="n">
         <v>0</v>
       </c>
-      <c r="Z1078" t="inlineStr"/>
-      <c r="AA1078" t="inlineStr"/>
+      <c r="Z1078" t="n">
+        <v>93079.58479999991</v>
+      </c>
+      <c r="AA1078" t="n">
+        <v>0.4838286569363399</v>
+      </c>
     </row>
     <row r="1079">
       <c r="A1079" t="n">
@@ -86778,10 +86850,10 @@
         <v>0</v>
       </c>
       <c r="Z1082" t="n">
-        <v>77892.61120000006</v>
+        <v>78067.83000000006</v>
       </c>
       <c r="AA1082" t="n">
-        <v>0.2244443069570964</v>
+        <v>-7.456036745669428e-14</v>
       </c>
     </row>
     <row r="1083">
@@ -87335,10 +87407,10 @@
         <v>0</v>
       </c>
       <c r="Z1089" t="n">
-        <v>164394.6607000003</v>
+        <v>164466.6721000003</v>
       </c>
       <c r="AA1089" t="n">
-        <v>0.3246643290705445</v>
+        <v>0.281002567571892</v>
       </c>
     </row>
     <row r="1090">
@@ -87812,12 +87884,8 @@
       <c r="Y1095" t="n">
         <v>0</v>
       </c>
-      <c r="Z1095" t="n">
-        <v>79094.6569000001</v>
-      </c>
-      <c r="AA1095" t="n">
-        <v>-0.04564577881954688</v>
-      </c>
+      <c r="Z1095" t="inlineStr"/>
+      <c r="AA1095" t="inlineStr"/>
     </row>
     <row r="1096">
       <c r="A1096" t="n">
@@ -87895,8 +87963,12 @@
       <c r="Y1096" t="n">
         <v>0</v>
       </c>
-      <c r="Z1096" t="inlineStr"/>
-      <c r="AA1096" t="inlineStr"/>
+      <c r="Z1096" t="n">
+        <v>141346.5994000002</v>
+      </c>
+      <c r="AA1096" t="n">
+        <v>4.099562857175705</v>
+      </c>
     </row>
     <row r="1097">
       <c r="A1097" t="n">
@@ -87974,8 +88046,12 @@
       <c r="Y1097" t="n">
         <v>0</v>
       </c>
-      <c r="Z1097" t="inlineStr"/>
-      <c r="AA1097" t="inlineStr"/>
+      <c r="Z1097" t="n">
+        <v>173765.0784999998</v>
+      </c>
+      <c r="AA1097" t="n">
+        <v>-0.7025317578081196</v>
+      </c>
     </row>
     <row r="1098">
       <c r="A1098" t="n">
@@ -88132,12 +88208,8 @@
       <c r="Y1099" t="n">
         <v>0</v>
       </c>
-      <c r="Z1099" t="n">
-        <v>113466.9773</v>
-      </c>
-      <c r="AA1099" t="n">
-        <v>-0.04622625580231055</v>
-      </c>
+      <c r="Z1099" t="inlineStr"/>
+      <c r="AA1099" t="inlineStr"/>
     </row>
     <row r="1100">
       <c r="A1100" t="n">
@@ -88373,8 +88445,12 @@
       <c r="Y1102" t="n">
         <v>0</v>
       </c>
-      <c r="Z1102" t="inlineStr"/>
-      <c r="AA1102" t="inlineStr"/>
+      <c r="Z1102" t="n">
+        <v>127718.0078</v>
+      </c>
+      <c r="AA1102" t="n">
+        <v>-3.292426942436602</v>
+      </c>
     </row>
     <row r="1103">
       <c r="A1103" t="n">
@@ -88847,8 +88923,12 @@
       <c r="Y1108" t="n">
         <v>0</v>
       </c>
-      <c r="Z1108" t="inlineStr"/>
-      <c r="AA1108" t="inlineStr"/>
+      <c r="Z1108" t="n">
+        <v>79058.57000000011</v>
+      </c>
+      <c r="AA1108" t="n">
+        <v>-1.288454959387299e-13</v>
+      </c>
     </row>
     <row r="1109">
       <c r="A1109" t="n">
@@ -89005,12 +89085,8 @@
       <c r="Y1110" t="n">
         <v>0</v>
       </c>
-      <c r="Z1110" t="n">
-        <v>62577.71999999998</v>
-      </c>
-      <c r="AA1110" t="n">
-        <v>3.488122105207776e-14</v>
-      </c>
+      <c r="Z1110" t="inlineStr"/>
+      <c r="AA1110" t="inlineStr"/>
     </row>
     <row r="1111">
       <c r="A1111" t="n">
@@ -89088,12 +89164,8 @@
       <c r="Y1111" t="n">
         <v>0</v>
       </c>
-      <c r="Z1111" t="n">
-        <v>73058.59999999987</v>
-      </c>
-      <c r="AA1111" t="n">
-        <v>1.792632722982669e-13</v>
-      </c>
+      <c r="Z1111" t="inlineStr"/>
+      <c r="AA1111" t="inlineStr"/>
     </row>
     <row r="1112">
       <c r="A1112" t="n">
@@ -89408,12 +89480,8 @@
       <c r="Y1115" t="n">
         <v>0</v>
       </c>
-      <c r="Z1115" t="n">
-        <v>130373.6103000001</v>
-      </c>
-      <c r="AA1115" t="n">
-        <v>0.7478833856084863</v>
-      </c>
+      <c r="Z1115" t="inlineStr"/>
+      <c r="AA1115" t="inlineStr"/>
     </row>
     <row r="1116">
       <c r="A1116" t="n">
@@ -89491,12 +89559,8 @@
       <c r="Y1116" t="n">
         <v>0</v>
       </c>
-      <c r="Z1116" t="n">
-        <v>67716.94000000013</v>
-      </c>
-      <c r="AA1116" t="n">
-        <v>-1.934039504078325e-13</v>
-      </c>
+      <c r="Z1116" t="inlineStr"/>
+      <c r="AA1116" t="inlineStr"/>
     </row>
     <row r="1117">
       <c r="A1117" t="n">
@@ -89574,8 +89638,12 @@
       <c r="Y1117" t="n">
         <v>0</v>
       </c>
-      <c r="Z1117" t="inlineStr"/>
-      <c r="AA1117" t="inlineStr"/>
+      <c r="Z1117" t="n">
+        <v>201805.4702999998</v>
+      </c>
+      <c r="AA1117" t="n">
+        <v>2.551309328672631</v>
+      </c>
     </row>
     <row r="1118">
       <c r="A1118" t="n">
@@ -89890,12 +89958,8 @@
       <c r="Y1121" t="n">
         <v>0</v>
       </c>
-      <c r="Z1121" t="n">
-        <v>155814.9761000001</v>
-      </c>
-      <c r="AA1121" t="n">
-        <v>-11.71037824452333</v>
-      </c>
+      <c r="Z1121" t="inlineStr"/>
+      <c r="AA1121" t="inlineStr"/>
     </row>
     <row r="1122">
       <c r="A1122" t="n">
@@ -89973,8 +90037,12 @@
       <c r="Y1122" t="n">
         <v>0</v>
       </c>
-      <c r="Z1122" t="inlineStr"/>
-      <c r="AA1122" t="inlineStr"/>
+      <c r="Z1122" t="n">
+        <v>82667.25999999983</v>
+      </c>
+      <c r="AA1122" t="n">
+        <v>1.936329660763347e-13</v>
+      </c>
     </row>
     <row r="1123">
       <c r="A1123" t="n">
@@ -90131,8 +90199,12 @@
       <c r="Y1124" t="n">
         <v>0</v>
       </c>
-      <c r="Z1124" t="inlineStr"/>
-      <c r="AA1124" t="inlineStr"/>
+      <c r="Z1124" t="n">
+        <v>151962.0036000001</v>
+      </c>
+      <c r="AA1124" t="n">
+        <v>-1.321255220182891</v>
+      </c>
     </row>
     <row r="1125">
       <c r="A1125" t="n">
@@ -90447,12 +90519,8 @@
       <c r="Y1128" t="n">
         <v>0</v>
       </c>
-      <c r="Z1128" t="n">
-        <v>289359.9981</v>
-      </c>
-      <c r="AA1128" t="n">
-        <v>15.1706668220034</v>
-      </c>
+      <c r="Z1128" t="inlineStr"/>
+      <c r="AA1128" t="inlineStr"/>
     </row>
     <row r="1129">
       <c r="A1129" t="n">
@@ -90609,8 +90677,12 @@
       <c r="Y1130" t="n">
         <v>0</v>
       </c>
-      <c r="Z1130" t="inlineStr"/>
-      <c r="AA1130" t="inlineStr"/>
+      <c r="Z1130" t="n">
+        <v>129146.9173999999</v>
+      </c>
+      <c r="AA1130" t="n">
+        <v>-0.359833287575109</v>
+      </c>
     </row>
     <row r="1131">
       <c r="A1131" t="n">
@@ -91399,12 +91471,8 @@
       <c r="Y1140" t="n">
         <v>0</v>
       </c>
-      <c r="Z1140" t="n">
-        <v>162648.818</v>
-      </c>
-      <c r="AA1140" t="n">
-        <v>-0.3879440516917918</v>
-      </c>
+      <c r="Z1140" t="inlineStr"/>
+      <c r="AA1140" t="inlineStr"/>
     </row>
     <row r="1141">
       <c r="A1141" t="n">
@@ -91956,8 +92024,12 @@
       <c r="Y1147" t="n">
         <v>0</v>
       </c>
-      <c r="Z1147" t="inlineStr"/>
-      <c r="AA1147" t="inlineStr"/>
+      <c r="Z1147" t="n">
+        <v>157775.8576</v>
+      </c>
+      <c r="AA1147" t="n">
+        <v>0.6453138533086009</v>
+      </c>
     </row>
     <row r="1148">
       <c r="A1148" t="n">
@@ -92035,8 +92107,12 @@
       <c r="Y1148" t="n">
         <v>0</v>
       </c>
-      <c r="Z1148" t="inlineStr"/>
-      <c r="AA1148" t="inlineStr"/>
+      <c r="Z1148" t="n">
+        <v>162984.4447000003</v>
+      </c>
+      <c r="AA1148" t="n">
+        <v>-3.331952293614677</v>
+      </c>
     </row>
     <row r="1149">
       <c r="A1149" t="n">
@@ -92272,12 +92348,8 @@
       <c r="Y1151" t="n">
         <v>0</v>
       </c>
-      <c r="Z1151" t="n">
-        <v>67716.94000000013</v>
-      </c>
-      <c r="AA1151" t="n">
-        <v>-1.934039504078325e-13</v>
-      </c>
+      <c r="Z1151" t="inlineStr"/>
+      <c r="AA1151" t="inlineStr"/>
     </row>
     <row r="1152">
       <c r="A1152" t="n">
@@ -92671,12 +92743,8 @@
       <c r="Y1156" t="n">
         <v>0</v>
       </c>
-      <c r="Z1156" t="n">
-        <v>45781.34140000003</v>
-      </c>
-      <c r="AA1156" t="n">
-        <v>-1.356677157004207</v>
-      </c>
+      <c r="Z1156" t="inlineStr"/>
+      <c r="AA1156" t="inlineStr"/>
     </row>
     <row r="1157">
       <c r="A1157" t="n">
@@ -92754,12 +92822,8 @@
       <c r="Y1157" t="n">
         <v>0</v>
       </c>
-      <c r="Z1157" t="n">
-        <v>133258.8183999999</v>
-      </c>
-      <c r="AA1157" t="n">
-        <v>-1.481276058781293</v>
-      </c>
+      <c r="Z1157" t="inlineStr"/>
+      <c r="AA1157" t="inlineStr"/>
     </row>
     <row r="1158">
       <c r="A1158" t="n">
@@ -92916,12 +92980,8 @@
       <c r="Y1159" t="n">
         <v>0</v>
       </c>
-      <c r="Z1159" t="n">
-        <v>79058.57000000011</v>
-      </c>
-      <c r="AA1159" t="n">
-        <v>-1.288454959387299e-13</v>
-      </c>
+      <c r="Z1159" t="inlineStr"/>
+      <c r="AA1159" t="inlineStr"/>
     </row>
     <row r="1160">
       <c r="A1160" t="n">
@@ -93161,12 +93221,8 @@
       <c r="Y1162" t="n">
         <v>0</v>
       </c>
-      <c r="Z1162" t="n">
-        <v>82667.25999999983</v>
-      </c>
-      <c r="AA1162" t="n">
-        <v>1.936329660763347e-13</v>
-      </c>
+      <c r="Z1162" t="inlineStr"/>
+      <c r="AA1162" t="inlineStr"/>
     </row>
     <row r="1163">
       <c r="A1163" t="n">
@@ -93244,8 +93300,12 @@
       <c r="Y1163" t="n">
         <v>0</v>
       </c>
-      <c r="Z1163" t="inlineStr"/>
-      <c r="AA1163" t="inlineStr"/>
+      <c r="Z1163" t="n">
+        <v>153470.5923000001</v>
+      </c>
+      <c r="AA1163" t="n">
+        <v>-0.4867451901168188</v>
+      </c>
     </row>
     <row r="1164">
       <c r="A1164" t="n">
@@ -93323,8 +93383,12 @@
       <c r="Y1164" t="n">
         <v>0</v>
       </c>
-      <c r="Z1164" t="inlineStr"/>
-      <c r="AA1164" t="inlineStr"/>
+      <c r="Z1164" t="n">
+        <v>82667.25999999983</v>
+      </c>
+      <c r="AA1164" t="n">
+        <v>1.936329660763347e-13</v>
+      </c>
     </row>
     <row r="1165">
       <c r="A1165" t="n">
@@ -93402,8 +93466,12 @@
       <c r="Y1165" t="n">
         <v>0</v>
       </c>
-      <c r="Z1165" t="inlineStr"/>
-      <c r="AA1165" t="inlineStr"/>
+      <c r="Z1165" t="n">
+        <v>67716.94000000013</v>
+      </c>
+      <c r="AA1165" t="n">
+        <v>-1.934039504078325e-13</v>
+      </c>
     </row>
     <row r="1166">
       <c r="A1166" t="n">
@@ -93560,12 +93628,8 @@
       <c r="Y1167" t="n">
         <v>0</v>
       </c>
-      <c r="Z1167" t="n">
-        <v>105234.1385</v>
-      </c>
-      <c r="AA1167" t="n">
-        <v>-2.295147757357245</v>
-      </c>
+      <c r="Z1167" t="inlineStr"/>
+      <c r="AA1167" t="inlineStr"/>
     </row>
     <row r="1168">
       <c r="A1168" t="n">
@@ -93722,12 +93786,8 @@
       <c r="Y1169" t="n">
         <v>0</v>
       </c>
-      <c r="Z1169" t="n">
-        <v>147196.4123999998</v>
-      </c>
-      <c r="AA1169" t="n">
-        <v>-0.9149495909998341</v>
-      </c>
+      <c r="Z1169" t="inlineStr"/>
+      <c r="AA1169" t="inlineStr"/>
     </row>
     <row r="1170">
       <c r="A1170" t="n">
@@ -93805,12 +93865,8 @@
       <c r="Y1170" t="n">
         <v>0</v>
       </c>
-      <c r="Z1170" t="n">
-        <v>95052.21939999994</v>
-      </c>
-      <c r="AA1170" t="n">
-        <v>0.263548442505619</v>
-      </c>
+      <c r="Z1170" t="inlineStr"/>
+      <c r="AA1170" t="inlineStr"/>
     </row>
     <row r="1171">
       <c r="A1171" t="n">
@@ -93888,12 +93944,8 @@
       <c r="Y1171" t="n">
         <v>0</v>
       </c>
-      <c r="Z1171" t="n">
-        <v>15151.73090000001</v>
-      </c>
-      <c r="AA1171" t="n">
-        <v>-2.266002294816504</v>
-      </c>
+      <c r="Z1171" t="inlineStr"/>
+      <c r="AA1171" t="inlineStr"/>
     </row>
     <row r="1172">
       <c r="A1172" t="n">
@@ -94129,12 +94181,8 @@
       <c r="Y1174" t="n">
         <v>0</v>
       </c>
-      <c r="Z1174" t="n">
-        <v>82667.25999999983</v>
-      </c>
-      <c r="AA1174" t="n">
-        <v>1.936329660763347e-13</v>
-      </c>
+      <c r="Z1174" t="inlineStr"/>
+      <c r="AA1174" t="inlineStr"/>
     </row>
     <row r="1175">
       <c r="A1175" t="n">
@@ -94212,12 +94260,8 @@
       <c r="Y1175" t="n">
         <v>0</v>
       </c>
-      <c r="Z1175" t="n">
-        <v>82516.95679999984</v>
-      </c>
-      <c r="AA1175" t="n">
-        <v>0.1818170821195174</v>
-      </c>
+      <c r="Z1175" t="inlineStr"/>
+      <c r="AA1175" t="inlineStr"/>
     </row>
     <row r="1176">
       <c r="A1176" t="n">
@@ -94295,8 +94339,12 @@
       <c r="Y1176" t="n">
         <v>0</v>
       </c>
-      <c r="Z1176" t="inlineStr"/>
-      <c r="AA1176" t="inlineStr"/>
+      <c r="Z1176" t="n">
+        <v>118399.5345</v>
+      </c>
+      <c r="AA1176" t="n">
+        <v>-0.180498638546725</v>
+      </c>
     </row>
     <row r="1177">
       <c r="A1177" t="n">
@@ -95006,12 +95054,8 @@
       <c r="Y1185" t="n">
         <v>0</v>
       </c>
-      <c r="Z1185" t="n">
-        <v>129083.2000000001</v>
-      </c>
-      <c r="AA1185" t="n">
-        <v>-0.1846633562877906</v>
-      </c>
+      <c r="Z1185" t="inlineStr"/>
+      <c r="AA1185" t="inlineStr"/>
     </row>
     <row r="1186">
       <c r="A1186" t="n">
@@ -95089,12 +95133,8 @@
       <c r="Y1186" t="n">
         <v>0</v>
       </c>
-      <c r="Z1186" t="n">
-        <v>57623.08949999997</v>
-      </c>
-      <c r="AA1186" t="n">
-        <v>2.075008866647885</v>
-      </c>
+      <c r="Z1186" t="inlineStr"/>
+      <c r="AA1186" t="inlineStr"/>
     </row>
     <row r="1187">
       <c r="A1187" t="n">
@@ -95172,12 +95212,8 @@
       <c r="Y1187" t="n">
         <v>0</v>
       </c>
-      <c r="Z1187" t="n">
-        <v>67716.94000000013</v>
-      </c>
-      <c r="AA1187" t="n">
-        <v>-1.934039504078325e-13</v>
-      </c>
+      <c r="Z1187" t="inlineStr"/>
+      <c r="AA1187" t="inlineStr"/>
     </row>
     <row r="1188">
       <c r="A1188" t="n">
@@ -95334,12 +95370,8 @@
       <c r="Y1189" t="n">
         <v>0</v>
       </c>
-      <c r="Z1189" t="n">
-        <v>140604.0314999999</v>
-      </c>
-      <c r="AA1189" t="n">
-        <v>0.4713308314554449</v>
-      </c>
+      <c r="Z1189" t="inlineStr"/>
+      <c r="AA1189" t="inlineStr"/>
     </row>
     <row r="1190">
       <c r="A1190" t="n">
@@ -95891,12 +95923,8 @@
       <c r="Y1196" t="n">
         <v>0</v>
       </c>
-      <c r="Z1196" t="n">
-        <v>79058.57000000011</v>
-      </c>
-      <c r="AA1196" t="n">
-        <v>-1.288454959387299e-13</v>
-      </c>
+      <c r="Z1196" t="inlineStr"/>
+      <c r="AA1196" t="inlineStr"/>
     </row>
     <row r="1197">
       <c r="A1197" t="n">
@@ -95974,12 +96002,8 @@
       <c r="Y1197" t="n">
         <v>0</v>
       </c>
-      <c r="Z1197" t="n">
-        <v>126749.8134</v>
-      </c>
-      <c r="AA1197" t="n">
-        <v>1.144777605449221</v>
-      </c>
+      <c r="Z1197" t="inlineStr"/>
+      <c r="AA1197" t="inlineStr"/>
     </row>
     <row r="1198">
       <c r="A1198" t="n">
@@ -96057,8 +96081,12 @@
       <c r="Y1198" t="n">
         <v>0</v>
       </c>
-      <c r="Z1198" t="inlineStr"/>
-      <c r="AA1198" t="inlineStr"/>
+      <c r="Z1198" t="n">
+        <v>79058.57000000011</v>
+      </c>
+      <c r="AA1198" t="n">
+        <v>-1.288454959387299e-13</v>
+      </c>
     </row>
     <row r="1199">
       <c r="A1199" t="n">
@@ -96136,12 +96164,8 @@
       <c r="Y1199" t="n">
         <v>0</v>
       </c>
-      <c r="Z1199" t="n">
-        <v>160033.8551999999</v>
-      </c>
-      <c r="AA1199" t="n">
-        <v>2.556916520390949</v>
-      </c>
+      <c r="Z1199" t="inlineStr"/>
+      <c r="AA1199" t="inlineStr"/>
     </row>
     <row r="1200">
       <c r="A1200" t="n">
@@ -96377,8 +96401,12 @@
       <c r="Y1202" t="n">
         <v>0</v>
       </c>
-      <c r="Z1202" t="inlineStr"/>
-      <c r="AA1202" t="inlineStr"/>
+      <c r="Z1202" t="n">
+        <v>101389.2642</v>
+      </c>
+      <c r="AA1202" t="n">
+        <v>0.9584174722380582</v>
+      </c>
     </row>
     <row r="1203">
       <c r="A1203" t="n">
@@ -96851,8 +96879,12 @@
       <c r="Y1208" t="n">
         <v>0</v>
       </c>
-      <c r="Z1208" t="inlineStr"/>
-      <c r="AA1208" t="inlineStr"/>
+      <c r="Z1208" t="n">
+        <v>121130.8986</v>
+      </c>
+      <c r="AA1208" t="n">
+        <v>0.4199311239540798</v>
+      </c>
     </row>
     <row r="1209">
       <c r="A1209" t="n">
@@ -97088,12 +97120,8 @@
       <c r="Y1211" t="n">
         <v>0</v>
       </c>
-      <c r="Z1211" t="n">
-        <v>170302.6243</v>
-      </c>
-      <c r="AA1211" t="n">
-        <v>-3.27582114989518</v>
-      </c>
+      <c r="Z1211" t="inlineStr"/>
+      <c r="AA1211" t="inlineStr"/>
     </row>
     <row r="1212">
       <c r="A1212" t="n">
@@ -97251,10 +97279,10 @@
         <v>0</v>
       </c>
       <c r="Z1213" t="n">
-        <v>96721.97629999999</v>
+        <v>95405.01989999997</v>
       </c>
       <c r="AA1213" t="n">
-        <v>3.356005738969233</v>
+        <v>4.67190034361277</v>
       </c>
     </row>
     <row r="1214">
@@ -97333,12 +97361,8 @@
       <c r="Y1214" t="n">
         <v>0</v>
       </c>
-      <c r="Z1214" t="n">
-        <v>22661.38150000004</v>
-      </c>
-      <c r="AA1214" t="n">
-        <v>-0.3946051600391728</v>
-      </c>
+      <c r="Z1214" t="inlineStr"/>
+      <c r="AA1214" t="inlineStr"/>
     </row>
     <row r="1215">
       <c r="A1215" t="n">
@@ -97416,12 +97440,8 @@
       <c r="Y1215" t="n">
         <v>0</v>
       </c>
-      <c r="Z1215" t="n">
-        <v>47339.46699999999</v>
-      </c>
-      <c r="AA1215" t="n">
-        <v>1.468852858913237</v>
-      </c>
+      <c r="Z1215" t="inlineStr"/>
+      <c r="AA1215" t="inlineStr"/>
     </row>
     <row r="1216">
       <c r="A1216" t="n">
@@ -98289,12 +98309,8 @@
       <c r="Y1226" t="n">
         <v>0</v>
       </c>
-      <c r="Z1226" t="n">
-        <v>289298.6029999998</v>
-      </c>
-      <c r="AA1226" t="n">
-        <v>-4.662906212430032</v>
-      </c>
+      <c r="Z1226" t="inlineStr"/>
+      <c r="AA1226" t="inlineStr"/>
     </row>
     <row r="1227">
       <c r="A1227" t="n">
@@ -98451,12 +98467,8 @@
       <c r="Y1228" t="n">
         <v>0</v>
       </c>
-      <c r="Z1228" t="n">
-        <v>89787.17660000004</v>
-      </c>
-      <c r="AA1228" t="n">
-        <v>-20.87949918044654</v>
-      </c>
+      <c r="Z1228" t="inlineStr"/>
+      <c r="AA1228" t="inlineStr"/>
     </row>
     <row r="1229">
       <c r="A1229" t="n">
@@ -98613,8 +98625,12 @@
       <c r="Y1230" t="n">
         <v>0</v>
       </c>
-      <c r="Z1230" t="inlineStr"/>
-      <c r="AA1230" t="inlineStr"/>
+      <c r="Z1230" t="n">
+        <v>100116.2531</v>
+      </c>
+      <c r="AA1230" t="n">
+        <v>0.6830004538476304</v>
+      </c>
     </row>
     <row r="1231">
       <c r="A1231" t="n">
@@ -98692,12 +98708,8 @@
       <c r="Y1231" t="n">
         <v>0</v>
       </c>
-      <c r="Z1231" t="n">
-        <v>123010.8664</v>
-      </c>
-      <c r="AA1231" t="n">
-        <v>1.334017570939383</v>
-      </c>
+      <c r="Z1231" t="inlineStr"/>
+      <c r="AA1231" t="inlineStr"/>
     </row>
     <row r="1232">
       <c r="A1232" t="n">
@@ -98775,8 +98787,12 @@
       <c r="Y1232" t="n">
         <v>0</v>
       </c>
-      <c r="Z1232" t="inlineStr"/>
-      <c r="AA1232" t="inlineStr"/>
+      <c r="Z1232" t="n">
+        <v>129308.0855</v>
+      </c>
+      <c r="AA1232" t="n">
+        <v>0.1075684604695648</v>
+      </c>
     </row>
     <row r="1233">
       <c r="A1233" t="n">
@@ -98933,12 +98949,8 @@
       <c r="Y1234" t="n">
         <v>0</v>
       </c>
-      <c r="Z1234" t="n">
-        <v>144952.4712999999</v>
-      </c>
-      <c r="AA1234" t="n">
-        <v>-0.2511050602602627</v>
-      </c>
+      <c r="Z1234" t="inlineStr"/>
+      <c r="AA1234" t="inlineStr"/>
     </row>
     <row r="1235">
       <c r="A1235" t="n">
@@ -99569,8 +99581,12 @@
       <c r="Y1242" t="n">
         <v>0</v>
       </c>
-      <c r="Z1242" t="inlineStr"/>
-      <c r="AA1242" t="inlineStr"/>
+      <c r="Z1242" t="n">
+        <v>165931.3269999999</v>
+      </c>
+      <c r="AA1242" t="n">
+        <v>-1.902112727780932</v>
+      </c>
     </row>
     <row r="1243">
       <c r="A1243" t="n">
@@ -99727,12 +99743,8 @@
       <c r="Y1244" t="n">
         <v>0</v>
       </c>
-      <c r="Z1244" t="n">
-        <v>99536.12789999998</v>
-      </c>
-      <c r="AA1244" t="n">
-        <v>-0.07402578861377672</v>
-      </c>
+      <c r="Z1244" t="inlineStr"/>
+      <c r="AA1244" t="inlineStr"/>
     </row>
     <row r="1245">
       <c r="A1245" t="n">
@@ -100205,12 +100217,8 @@
       <c r="Y1250" t="n">
         <v>0</v>
       </c>
-      <c r="Z1250" t="n">
-        <v>126171.9704</v>
-      </c>
-      <c r="AA1250" t="n">
-        <v>1.261596494524445</v>
-      </c>
+      <c r="Z1250" t="inlineStr"/>
+      <c r="AA1250" t="inlineStr"/>
     </row>
     <row r="1251">
       <c r="A1251" t="n">
@@ -100288,8 +100296,12 @@
       <c r="Y1251" t="n">
         <v>0</v>
       </c>
-      <c r="Z1251" t="inlineStr"/>
-      <c r="AA1251" t="inlineStr"/>
+      <c r="Z1251" t="n">
+        <v>310797.6831999998</v>
+      </c>
+      <c r="AA1251" t="n">
+        <v>20.54884814910675</v>
+      </c>
     </row>
     <row r="1252">
       <c r="A1252" t="n">
@@ -100446,8 +100458,12 @@
       <c r="Y1253" t="n">
         <v>0</v>
       </c>
-      <c r="Z1253" t="inlineStr"/>
-      <c r="AA1253" t="inlineStr"/>
+      <c r="Z1253" t="n">
+        <v>169330.8114</v>
+      </c>
+      <c r="AA1253" t="n">
+        <v>4.03761437734407</v>
+      </c>
     </row>
     <row r="1254">
       <c r="A1254" t="n">
@@ -100525,8 +100541,12 @@
       <c r="Y1254" t="n">
         <v>0</v>
       </c>
-      <c r="Z1254" t="inlineStr"/>
-      <c r="AA1254" t="inlineStr"/>
+      <c r="Z1254" t="n">
+        <v>128020.6922</v>
+      </c>
+      <c r="AA1254" t="n">
+        <v>-0.3779498702589257</v>
+      </c>
     </row>
     <row r="1255">
       <c r="A1255" t="n">
@@ -100841,12 +100861,8 @@
       <c r="Y1258" t="n">
         <v>0</v>
       </c>
-      <c r="Z1258" t="n">
-        <v>100804.6226</v>
-      </c>
-      <c r="AA1258" t="n">
-        <v>-0.1463307242502573</v>
-      </c>
+      <c r="Z1258" t="inlineStr"/>
+      <c r="AA1258" t="inlineStr"/>
     </row>
     <row r="1259">
       <c r="A1259" t="n">
@@ -101161,12 +101177,8 @@
       <c r="Y1262" t="n">
         <v>0</v>
       </c>
-      <c r="Z1262" t="n">
-        <v>88156.48189999997</v>
-      </c>
-      <c r="AA1262" t="n">
-        <v>-8.283265760044698</v>
-      </c>
+      <c r="Z1262" t="inlineStr"/>
+      <c r="AA1262" t="inlineStr"/>
     </row>
     <row r="1263">
       <c r="A1263" t="n">
@@ -101481,8 +101493,12 @@
       <c r="Y1266" t="n">
         <v>0</v>
       </c>
-      <c r="Z1266" t="inlineStr"/>
-      <c r="AA1266" t="inlineStr"/>
+      <c r="Z1266" t="n">
+        <v>126626.8483</v>
+      </c>
+      <c r="AA1266" t="n">
+        <v>-0.2350974848778518</v>
+      </c>
     </row>
     <row r="1267">
       <c r="A1267" t="n">
@@ -101801,12 +101817,8 @@
       <c r="Y1270" t="n">
         <v>0</v>
       </c>
-      <c r="Z1270" t="n">
-        <v>141414.2445999999</v>
-      </c>
-      <c r="AA1270" t="n">
-        <v>-0.7603753494550511</v>
-      </c>
+      <c r="Z1270" t="inlineStr"/>
+      <c r="AA1270" t="inlineStr"/>
     </row>
     <row r="1271">
       <c r="A1271" t="n">
@@ -101884,8 +101896,12 @@
       <c r="Y1271" t="n">
         <v>0</v>
       </c>
-      <c r="Z1271" t="inlineStr"/>
-      <c r="AA1271" t="inlineStr"/>
+      <c r="Z1271" t="n">
+        <v>124212.9421000001</v>
+      </c>
+      <c r="AA1271" t="n">
+        <v>-0.2427058029799014</v>
+      </c>
     </row>
     <row r="1272">
       <c r="A1272" t="n">
@@ -102121,12 +102137,8 @@
       <c r="Y1274" t="n">
         <v>0</v>
       </c>
-      <c r="Z1274" t="n">
-        <v>180145.09</v>
-      </c>
-      <c r="AA1274" t="n">
-        <v>-6.776589191911237</v>
-      </c>
+      <c r="Z1274" t="inlineStr"/>
+      <c r="AA1274" t="inlineStr"/>
     </row>
     <row r="1275">
       <c r="A1275" t="n">
@@ -102204,8 +102216,12 @@
       <c r="Y1275" t="n">
         <v>0</v>
       </c>
-      <c r="Z1275" t="inlineStr"/>
-      <c r="AA1275" t="inlineStr"/>
+      <c r="Z1275" t="n">
+        <v>146386.5574000001</v>
+      </c>
+      <c r="AA1275" t="n">
+        <v>0.5036057840987729</v>
+      </c>
     </row>
     <row r="1276">
       <c r="A1276" t="n">
@@ -102283,8 +102299,12 @@
       <c r="Y1276" t="n">
         <v>0</v>
       </c>
-      <c r="Z1276" t="inlineStr"/>
-      <c r="AA1276" t="inlineStr"/>
+      <c r="Z1276" t="n">
+        <v>129059.801</v>
+      </c>
+      <c r="AA1276" t="n">
+        <v>-0.2921352924807102</v>
+      </c>
     </row>
     <row r="1277">
       <c r="A1277" t="n">
@@ -102441,12 +102461,8 @@
       <c r="Y1278" t="n">
         <v>0</v>
       </c>
-      <c r="Z1278" t="n">
-        <v>112270.5911999998</v>
-      </c>
-      <c r="AA1278" t="n">
-        <v>-1.497448971289267</v>
-      </c>
+      <c r="Z1278" t="inlineStr"/>
+      <c r="AA1278" t="inlineStr"/>
     </row>
     <row r="1279">
       <c r="A1279" t="n">
@@ -102603,12 +102619,8 @@
       <c r="Y1280" t="n">
         <v>0</v>
       </c>
-      <c r="Z1280" t="n">
-        <v>82793.62129999984</v>
-      </c>
-      <c r="AA1280" t="n">
-        <v>-0.1528553141834434</v>
-      </c>
+      <c r="Z1280" t="inlineStr"/>
+      <c r="AA1280" t="inlineStr"/>
     </row>
     <row r="1281">
       <c r="A1281" t="n">
@@ -102844,12 +102856,8 @@
       <c r="Y1283" t="n">
         <v>0</v>
       </c>
-      <c r="Z1283" t="n">
-        <v>136244.2048</v>
-      </c>
-      <c r="AA1283" t="n">
-        <v>2.628419245759433</v>
-      </c>
+      <c r="Z1283" t="inlineStr"/>
+      <c r="AA1283" t="inlineStr"/>
     </row>
     <row r="1284">
       <c r="A1284" t="n">
@@ -103006,8 +103014,12 @@
       <c r="Y1285" t="n">
         <v>0</v>
       </c>
-      <c r="Z1285" t="inlineStr"/>
-      <c r="AA1285" t="inlineStr"/>
+      <c r="Z1285" t="n">
+        <v>129885.3057</v>
+      </c>
+      <c r="AA1285" t="n">
+        <v>-2.364368771883445</v>
+      </c>
     </row>
     <row r="1286">
       <c r="A1286" t="n">
@@ -103164,12 +103176,8 @@
       <c r="Y1287" t="n">
         <v>0</v>
       </c>
-      <c r="Z1287" t="n">
-        <v>129161.9253000001</v>
-      </c>
-      <c r="AA1287" t="n">
-        <v>0.8668987566486678</v>
-      </c>
+      <c r="Z1287" t="inlineStr"/>
+      <c r="AA1287" t="inlineStr"/>
     </row>
     <row r="1288">
       <c r="A1288" t="n">
@@ -103326,12 +103334,8 @@
       <c r="Y1289" t="n">
         <v>0</v>
       </c>
-      <c r="Z1289" t="n">
-        <v>67716.94000000013</v>
-      </c>
-      <c r="AA1289" t="n">
-        <v>-1.934039504078325e-13</v>
-      </c>
+      <c r="Z1289" t="inlineStr"/>
+      <c r="AA1289" t="inlineStr"/>
     </row>
     <row r="1290">
       <c r="A1290" t="n">
@@ -103646,8 +103650,12 @@
       <c r="Y1293" t="n">
         <v>0</v>
       </c>
-      <c r="Z1293" t="inlineStr"/>
-      <c r="AA1293" t="inlineStr"/>
+      <c r="Z1293" t="n">
+        <v>67716.94000000013</v>
+      </c>
+      <c r="AA1293" t="n">
+        <v>-1.934039504078325e-13</v>
+      </c>
     </row>
     <row r="1294">
       <c r="A1294" t="n">
@@ -103725,12 +103733,8 @@
       <c r="Y1294" t="n">
         <v>0</v>
       </c>
-      <c r="Z1294" t="n">
-        <v>79058.57000000011</v>
-      </c>
-      <c r="AA1294" t="n">
-        <v>-1.288454959387299e-13</v>
-      </c>
+      <c r="Z1294" t="inlineStr"/>
+      <c r="AA1294" t="inlineStr"/>
     </row>
     <row r="1295">
       <c r="A1295" t="n">
@@ -103808,8 +103812,12 @@
       <c r="Y1295" t="n">
         <v>0</v>
       </c>
-      <c r="Z1295" t="inlineStr"/>
-      <c r="AA1295" t="inlineStr"/>
+      <c r="Z1295" t="n">
+        <v>79058.57000000011</v>
+      </c>
+      <c r="AA1295" t="n">
+        <v>-1.288454959387299e-13</v>
+      </c>
     </row>
     <row r="1296">
       <c r="A1296" t="n">
@@ -104203,8 +104211,12 @@
       <c r="Y1300" t="n">
         <v>0</v>
       </c>
-      <c r="Z1300" t="inlineStr"/>
-      <c r="AA1300" t="inlineStr"/>
+      <c r="Z1300" t="n">
+        <v>67716.94000000013</v>
+      </c>
+      <c r="AA1300" t="n">
+        <v>-1.934039504078325e-13</v>
+      </c>
     </row>
     <row r="1301">
       <c r="A1301" t="n">
@@ -104282,12 +104294,8 @@
       <c r="Y1301" t="n">
         <v>0</v>
       </c>
-      <c r="Z1301" t="n">
-        <v>129382.8615</v>
-      </c>
-      <c r="AA1301" t="n">
-        <v>-3.072420276982869</v>
-      </c>
+      <c r="Z1301" t="inlineStr"/>
+      <c r="AA1301" t="inlineStr"/>
     </row>
     <row r="1302">
       <c r="A1302" t="n">
@@ -104365,12 +104373,8 @@
       <c r="Y1302" t="n">
         <v>0</v>
       </c>
-      <c r="Z1302" t="n">
-        <v>82667.25999999983</v>
-      </c>
-      <c r="AA1302" t="n">
-        <v>1.936329660763347e-13</v>
-      </c>
+      <c r="Z1302" t="inlineStr"/>
+      <c r="AA1302" t="inlineStr"/>
     </row>
     <row r="1303">
       <c r="A1303" t="n">
@@ -104527,12 +104531,8 @@
       <c r="Y1304" t="n">
         <v>0</v>
       </c>
-      <c r="Z1304" t="n">
-        <v>125189.6565</v>
-      </c>
-      <c r="AA1304" t="n">
-        <v>0.7216384598718704</v>
-      </c>
+      <c r="Z1304" t="inlineStr"/>
+      <c r="AA1304" t="inlineStr"/>
     </row>
     <row r="1305">
       <c r="A1305" t="n">
@@ -104689,12 +104689,8 @@
       <c r="Y1306" t="n">
         <v>0</v>
       </c>
-      <c r="Z1306" t="n">
-        <v>143429.3497</v>
-      </c>
-      <c r="AA1306" t="n">
-        <v>0.1750895665200712</v>
-      </c>
+      <c r="Z1306" t="inlineStr"/>
+      <c r="AA1306" t="inlineStr"/>
     </row>
     <row r="1307">
       <c r="A1307" t="n">
@@ -105167,12 +105163,8 @@
       <c r="Y1312" t="n">
         <v>0</v>
       </c>
-      <c r="Z1312" t="n">
-        <v>67716.94000000013</v>
-      </c>
-      <c r="AA1312" t="n">
-        <v>-1.934039504078325e-13</v>
-      </c>
+      <c r="Z1312" t="inlineStr"/>
+      <c r="AA1312" t="inlineStr"/>
     </row>
     <row r="1313">
       <c r="A1313" t="n">
@@ -105250,8 +105242,12 @@
       <c r="Y1313" t="n">
         <v>0</v>
       </c>
-      <c r="Z1313" t="inlineStr"/>
-      <c r="AA1313" t="inlineStr"/>
+      <c r="Z1313" t="n">
+        <v>67716.94000000013</v>
+      </c>
+      <c r="AA1313" t="n">
+        <v>-1.934039504078325e-13</v>
+      </c>
     </row>
     <row r="1314">
       <c r="A1314" t="n">
@@ -105408,8 +105404,12 @@
       <c r="Y1315" t="n">
         <v>0</v>
       </c>
-      <c r="Z1315" t="inlineStr"/>
-      <c r="AA1315" t="inlineStr"/>
+      <c r="Z1315" t="n">
+        <v>138635.7564</v>
+      </c>
+      <c r="AA1315" t="n">
+        <v>-2.100869526280584</v>
+      </c>
     </row>
     <row r="1316">
       <c r="A1316" t="n">
